--- a/keel_trb_smart_template.xlsx
+++ b/keel_trb_smart_template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A068C57-7BE6-47F8-ADB3-6D12921EEBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCA34F7D-6FF7-47E9-965A-4FCA6DAC8549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TRB Tasks" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="99">
   <si>
     <t>Function (Select from List)</t>
   </si>
@@ -187,13 +187,139 @@
   </si>
   <si>
     <t>A-VI/6</t>
+  </si>
+  <si>
+    <t>International Regulations for Preventing Collisions at Sea</t>
+  </si>
+  <si>
+    <t>COLREGS</t>
+  </si>
+  <si>
+    <t>Rule 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learn and quote the COLREGS. Understand the legal implications and importance of each rule. </t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Rule 02</t>
+  </si>
+  <si>
+    <t>Rule 03</t>
+  </si>
+  <si>
+    <t>Rule 04</t>
+  </si>
+  <si>
+    <t>Rule 05</t>
+  </si>
+  <si>
+    <t>Rule 06</t>
+  </si>
+  <si>
+    <t>Rule 07</t>
+  </si>
+  <si>
+    <t>Rule 08</t>
+  </si>
+  <si>
+    <t>Rule 09</t>
+  </si>
+  <si>
+    <t>Rule 10</t>
+  </si>
+  <si>
+    <t>Rule 11</t>
+  </si>
+  <si>
+    <t>Rule 12</t>
+  </si>
+  <si>
+    <t>Rule 13</t>
+  </si>
+  <si>
+    <t>Rule 14</t>
+  </si>
+  <si>
+    <t>Rule 15</t>
+  </si>
+  <si>
+    <t>Rule 16</t>
+  </si>
+  <si>
+    <t>Rule 17</t>
+  </si>
+  <si>
+    <t>Rule 18</t>
+  </si>
+  <si>
+    <t>Rule 19</t>
+  </si>
+  <si>
+    <t>Rule 20</t>
+  </si>
+  <si>
+    <t>Rule 21</t>
+  </si>
+  <si>
+    <t>Rule 22</t>
+  </si>
+  <si>
+    <t>Rule 23</t>
+  </si>
+  <si>
+    <t>Rule 24</t>
+  </si>
+  <si>
+    <t>Rule 25</t>
+  </si>
+  <si>
+    <t>Rule 26</t>
+  </si>
+  <si>
+    <t>Rule 27</t>
+  </si>
+  <si>
+    <t>Rule 28</t>
+  </si>
+  <si>
+    <t>Rule 29</t>
+  </si>
+  <si>
+    <t>Rule 30</t>
+  </si>
+  <si>
+    <t>Rule 31</t>
+  </si>
+  <si>
+    <t>Rule 32</t>
+  </si>
+  <si>
+    <t>Rule 33</t>
+  </si>
+  <si>
+    <t>Rule 34</t>
+  </si>
+  <si>
+    <t>Rule 35</t>
+  </si>
+  <si>
+    <t>Rule 36</t>
+  </si>
+  <si>
+    <t>Rule 37</t>
+  </si>
+  <si>
+    <t>Rule 38</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,6 +332,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -575,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -632,7 +764,1566 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s">
+        <v>61</v>
+      </c>
+      <c r="J18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="s">
+        <v>61</v>
+      </c>
+      <c r="J19" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>61</v>
+      </c>
+      <c r="J21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J23" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>61</v>
+      </c>
+      <c r="J24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>61</v>
+      </c>
+      <c r="J25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>61</v>
+      </c>
+      <c r="J26" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="s">
+        <v>18</v>
+      </c>
+      <c r="M26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J27" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E28" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s">
+        <v>61</v>
+      </c>
+      <c r="J28" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s">
+        <v>61</v>
+      </c>
+      <c r="J29" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="s">
+        <v>18</v>
+      </c>
+      <c r="M29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s">
+        <v>61</v>
+      </c>
+      <c r="J30" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="s">
+        <v>18</v>
+      </c>
+      <c r="M30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s">
+        <v>61</v>
+      </c>
+      <c r="J31" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="s">
+        <v>18</v>
+      </c>
+      <c r="M31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s">
+        <v>61</v>
+      </c>
+      <c r="J32" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>61</v>
+      </c>
+      <c r="J33" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s">
+        <v>18</v>
+      </c>
+      <c r="M33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s">
+        <v>61</v>
+      </c>
+      <c r="J34" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="s">
+        <v>18</v>
+      </c>
+      <c r="M34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="s">
+        <v>18</v>
+      </c>
+      <c r="M35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" t="s">
+        <v>95</v>
+      </c>
+      <c r="E36" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s">
+        <v>61</v>
+      </c>
+      <c r="J36" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="s">
+        <v>18</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s">
+        <v>61</v>
+      </c>
+      <c r="J37" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="s">
+        <v>18</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>18</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="s">
+        <v>61</v>
+      </c>
+      <c r="J39" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>18</v>
+      </c>
+      <c r="M39" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="K2:K500" xr:uid="{00000000-0002-0000-0000-00000A000000}">
       <formula1>"TRUE,FALSE"</formula1>

--- a/keel_trb_smart_template.xlsx
+++ b/keel_trb_smart_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCA34F7D-6FF7-47E9-965A-4FCA6DAC8549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F695D5D-BFA6-47D9-8F5F-B1E3ECE9519A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="141">
   <si>
     <t>Function (Select from List)</t>
   </si>
@@ -313,6 +313,132 @@
   </si>
   <si>
     <t>Rule 38</t>
+  </si>
+  <si>
+    <t>Plan and conduct a passage and determine position</t>
+  </si>
+  <si>
+    <t>Consult Navigational publications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonstrate an understanding of the chart folio system and assist in correcting charts and other publications. </t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of contents and the use of Notices to mariners</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of contents and the use of Sailing directions and ship's routeing information</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of contents and the use of List of lights and fog signals</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of contents and the use of Tide tables, tidal stream and current atlases</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of contents and the use of Pilot books</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of contents and the use of Radio navigational warnings</t>
+  </si>
+  <si>
+    <t>Select charts of adequate scale</t>
+  </si>
+  <si>
+    <t>Assist deck officer in preparing navigational passages and in voyage planning</t>
+  </si>
+  <si>
+    <t>Select appropriate scale chart from paper chart portfolio, Electronic Chart System (ECSJ or Electronic Chart Display and Information Systems (ECDIS)</t>
+  </si>
+  <si>
+    <t>Set up Course Recorder</t>
+  </si>
+  <si>
+    <t>Set up Off course alarm</t>
+  </si>
+  <si>
+    <t>Calculate Estimated Time of Arrival (ETA)</t>
+  </si>
+  <si>
+    <t>Practise tidal calculations</t>
+  </si>
+  <si>
+    <t>Practise calculat ions for distance, average speed, course made good, set and drift, ETA</t>
+  </si>
+  <si>
+    <t>Determine and apply compass error for courses and compass bearings</t>
+  </si>
+  <si>
+    <t>Apply magnetic variation and deviation</t>
+  </si>
+  <si>
+    <t>Practise use of the azimuth mirror</t>
+  </si>
+  <si>
+    <t>Practice Azimuths</t>
+  </si>
+  <si>
+    <t>Practice Amplitudes</t>
+  </si>
+  <si>
+    <t>Understand the use of and make ent ries in the compass error book and interpre.t information recorded</t>
+  </si>
+  <si>
+    <t>Demonstrate the use of the compass when setting course</t>
+  </si>
+  <si>
+    <t>Estimate and make allowance for leeway and tidal currents</t>
+  </si>
+  <si>
+    <t>Set Courses</t>
+  </si>
+  <si>
+    <t>Recognise conspicusous objects and other terrestrial/celestial aids to navigation in daylight and at night</t>
+  </si>
+  <si>
+    <t>Perform look-out duties and report objects in degrees or points</t>
+  </si>
+  <si>
+    <t>Identify aids to navigation including lighthouses, beacons and buoys</t>
+  </si>
+  <si>
+    <t>Identify star constellations and stars of first magnitude and learn to use star chart and star finder</t>
+  </si>
+  <si>
+    <t>Practice compass bearings and visual fixes</t>
+  </si>
+  <si>
+    <t>Demostrate a knowledge of the IALA system of buoyage</t>
+  </si>
+  <si>
+    <t>Use azimuth mirror and sextant to fix ship's position by celestial and terrestrial observations</t>
+  </si>
+  <si>
+    <t>Use azimuth mirror to fix ship's position</t>
+  </si>
+  <si>
+    <t>Use a sextant and demonstrate how to identify and remove errors</t>
+  </si>
+  <si>
+    <t>Practice horizontal and vertical sextant angles</t>
+  </si>
+  <si>
+    <t>Make noon calculations e.g. distance, average speed, course made good, set and drift and ETA</t>
+  </si>
+  <si>
+    <t>State ship's position by dead reckoning</t>
+  </si>
+  <si>
+    <t>Operate all electronic navigational equipment to ascertain the ship's position</t>
+  </si>
+  <si>
+    <t>Practice Radar switch on and set up procedure</t>
+  </si>
+  <si>
+    <t>Practice Radar Plotting</t>
+  </si>
+  <si>
+    <t>Practice Position fixes by radar</t>
   </si>
 </sst>
 </file>
@@ -365,9 +491,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -707,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -2320,6 +2447,1336 @@
       </c>
       <c r="M39" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s">
+        <v>61</v>
+      </c>
+      <c r="J40" t="s">
+        <v>24</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>25</v>
+      </c>
+      <c r="M40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" t="s">
+        <v>100</v>
+      </c>
+      <c r="D41" t="s">
+        <v>102</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s">
+        <v>61</v>
+      </c>
+      <c r="J41" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s">
+        <v>100</v>
+      </c>
+      <c r="D42" t="s">
+        <v>103</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" t="s">
+        <v>61</v>
+      </c>
+      <c r="J42" t="s">
+        <v>24</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" t="s">
+        <v>104</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s">
+        <v>61</v>
+      </c>
+      <c r="J43" t="s">
+        <v>24</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="s">
+        <v>25</v>
+      </c>
+      <c r="M43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" t="s">
+        <v>105</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s">
+        <v>61</v>
+      </c>
+      <c r="J44" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" t="s">
+        <v>106</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s">
+        <v>61</v>
+      </c>
+      <c r="J45" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="s">
+        <v>25</v>
+      </c>
+      <c r="M45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47" t="s">
+        <v>109</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s">
+        <v>61</v>
+      </c>
+      <c r="J47" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="s">
+        <v>18</v>
+      </c>
+      <c r="M47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" t="s">
+        <v>110</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s">
+        <v>61</v>
+      </c>
+      <c r="J48" t="s">
+        <v>24</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="s">
+        <v>18</v>
+      </c>
+      <c r="M48" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" t="s">
+        <v>124</v>
+      </c>
+      <c r="D49" t="s">
+        <v>122</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" t="s">
+        <v>61</v>
+      </c>
+      <c r="J49" t="s">
+        <v>24</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="s">
+        <v>18</v>
+      </c>
+      <c r="M49" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J50" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="s">
+        <v>18</v>
+      </c>
+      <c r="M50" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" t="s">
+        <v>124</v>
+      </c>
+      <c r="D51" t="s">
+        <v>112</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s">
+        <v>61</v>
+      </c>
+      <c r="J51" t="s">
+        <v>24</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="s">
+        <v>18</v>
+      </c>
+      <c r="M51" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" t="s">
+        <v>123</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" t="s">
+        <v>61</v>
+      </c>
+      <c r="J52" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="s">
+        <v>18</v>
+      </c>
+      <c r="M52" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" t="s">
+        <v>124</v>
+      </c>
+      <c r="D53" t="s">
+        <v>114</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="s">
+        <v>61</v>
+      </c>
+      <c r="J53" t="s">
+        <v>24</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="s">
+        <v>18</v>
+      </c>
+      <c r="M53" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" t="s">
+        <v>99</v>
+      </c>
+      <c r="C54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" t="s">
+        <v>115</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" t="s">
+        <v>61</v>
+      </c>
+      <c r="J54" t="s">
+        <v>24</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="s">
+        <v>18</v>
+      </c>
+      <c r="M54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" t="s">
+        <v>99</v>
+      </c>
+      <c r="C55" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" t="s">
+        <v>117</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" t="s">
+        <v>61</v>
+      </c>
+      <c r="J55" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="s">
+        <v>18</v>
+      </c>
+      <c r="M55" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" t="s">
+        <v>118</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="s">
+        <v>61</v>
+      </c>
+      <c r="J56" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="s">
+        <v>18</v>
+      </c>
+      <c r="M56" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>13</v>
+      </c>
+      <c r="B57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57" t="s">
+        <v>119</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" t="s">
+        <v>61</v>
+      </c>
+      <c r="J57" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="s">
+        <v>18</v>
+      </c>
+      <c r="M57" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" t="s">
+        <v>120</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" t="s">
+        <v>61</v>
+      </c>
+      <c r="J58" t="s">
+        <v>24</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" t="s">
+        <v>18</v>
+      </c>
+      <c r="M58" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" t="s">
+        <v>121</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" t="s">
+        <v>61</v>
+      </c>
+      <c r="J59" t="s">
+        <v>24</v>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" t="s">
+        <v>18</v>
+      </c>
+      <c r="M59" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" t="s">
+        <v>125</v>
+      </c>
+      <c r="D60" t="s">
+        <v>126</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" t="s">
+        <v>61</v>
+      </c>
+      <c r="J60" t="s">
+        <v>24</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="s">
+        <v>18</v>
+      </c>
+      <c r="M60" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" t="s">
+        <v>125</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" t="s">
+        <v>61</v>
+      </c>
+      <c r="J61" t="s">
+        <v>24</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="s">
+        <v>18</v>
+      </c>
+      <c r="M61" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" t="s">
+        <v>99</v>
+      </c>
+      <c r="C62" t="s">
+        <v>125</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" t="s">
+        <v>61</v>
+      </c>
+      <c r="J62" t="s">
+        <v>24</v>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="s">
+        <v>18</v>
+      </c>
+      <c r="M62" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
+        <v>99</v>
+      </c>
+      <c r="C63" t="s">
+        <v>125</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63" t="s">
+        <v>61</v>
+      </c>
+      <c r="J63" t="s">
+        <v>24</v>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" t="s">
+        <v>18</v>
+      </c>
+      <c r="M63" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" t="s">
+        <v>125</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" t="s">
+        <v>61</v>
+      </c>
+      <c r="J64" t="s">
+        <v>24</v>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
+      <c r="L64" t="s">
+        <v>18</v>
+      </c>
+      <c r="M64" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" t="s">
+        <v>131</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F65" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" t="s">
+        <v>61</v>
+      </c>
+      <c r="J65" t="s">
+        <v>24</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" t="s">
+        <v>18</v>
+      </c>
+      <c r="M65" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
+        <v>99</v>
+      </c>
+      <c r="C66" t="s">
+        <v>131</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F66" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" t="s">
+        <v>61</v>
+      </c>
+      <c r="J66" t="s">
+        <v>24</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" t="s">
+        <v>18</v>
+      </c>
+      <c r="M66" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" t="s">
+        <v>99</v>
+      </c>
+      <c r="C67" t="s">
+        <v>131</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F67" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" t="s">
+        <v>16</v>
+      </c>
+      <c r="I67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J67" t="s">
+        <v>24</v>
+      </c>
+      <c r="K67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" t="s">
+        <v>18</v>
+      </c>
+      <c r="M67" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>13</v>
+      </c>
+      <c r="B68" t="s">
+        <v>99</v>
+      </c>
+      <c r="C68" t="s">
+        <v>131</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" t="s">
+        <v>61</v>
+      </c>
+      <c r="J68" t="s">
+        <v>24</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L68" t="s">
+        <v>18</v>
+      </c>
+      <c r="M68" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" t="s">
+        <v>99</v>
+      </c>
+      <c r="C69" t="s">
+        <v>136</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" t="s">
+        <v>61</v>
+      </c>
+      <c r="J69" t="s">
+        <v>24</v>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" t="s">
+        <v>18</v>
+      </c>
+      <c r="M69" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>13</v>
+      </c>
+      <c r="B70" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" t="s">
+        <v>136</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" t="s">
+        <v>61</v>
+      </c>
+      <c r="J70" t="s">
+        <v>24</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="s">
+        <v>18</v>
+      </c>
+      <c r="M70" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>13</v>
+      </c>
+      <c r="B71" t="s">
+        <v>99</v>
+      </c>
+      <c r="C71" t="s">
+        <v>137</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
+        <v>16</v>
+      </c>
+      <c r="I71" t="s">
+        <v>61</v>
+      </c>
+      <c r="J71" t="s">
+        <v>24</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" t="s">
+        <v>18</v>
+      </c>
+      <c r="M71" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>13</v>
+      </c>
+      <c r="B72" t="s">
+        <v>99</v>
+      </c>
+      <c r="C72" t="s">
+        <v>137</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" t="s">
+        <v>61</v>
+      </c>
+      <c r="J72" t="s">
+        <v>24</v>
+      </c>
+      <c r="K72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" t="s">
+        <v>18</v>
+      </c>
+      <c r="M72" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>13</v>
+      </c>
+      <c r="B73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C73" t="s">
+        <v>137</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" t="s">
+        <v>61</v>
+      </c>
+      <c r="J73" t="s">
+        <v>24</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+      <c r="L73" t="s">
+        <v>18</v>
+      </c>
+      <c r="M73" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" t="s">
+        <v>99</v>
+      </c>
+      <c r="C74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" t="s">
+        <v>16</v>
+      </c>
+      <c r="I74" t="s">
+        <v>61</v>
+      </c>
+      <c r="J74" t="s">
+        <v>24</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" t="s">
+        <v>18</v>
+      </c>
+      <c r="M74" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/keel_trb_smart_template.xlsx
+++ b/keel_trb_smart_template.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F695D5D-BFA6-47D9-8F5F-B1E3ECE9519A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883AF90D-6AD6-4198-A23F-B8027F3405A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="147">
   <si>
     <t>Function (Select from List)</t>
   </si>
@@ -439,6 +439,24 @@
   </si>
   <si>
     <t>Practice Position fixes by radar</t>
+  </si>
+  <si>
+    <t>Maintain a safe engineering watch</t>
+  </si>
+  <si>
+    <t>Relieve and hand over the watch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follow the correct procedure for handling over a watch at sea. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follow the correct procedure for handling over a watch in port. </t>
+  </si>
+  <si>
+    <t>Follow the correct procedure for taking over and accepting a watch at sea</t>
+  </si>
+  <si>
+    <t>Follow the correct procedure for taking over and accepting a watch in port</t>
   </si>
 </sst>
 </file>
@@ -491,10 +509,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -834,7 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3257,7 +3274,7 @@
       <c r="C61" t="s">
         <v>125</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" t="s">
         <v>127</v>
       </c>
       <c r="F61" t="s">
@@ -3295,7 +3312,7 @@
       <c r="C62" t="s">
         <v>125</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" t="s">
         <v>128</v>
       </c>
       <c r="F62" t="s">
@@ -3333,7 +3350,7 @@
       <c r="C63" t="s">
         <v>125</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" t="s">
         <v>129</v>
       </c>
       <c r="F63" t="s">
@@ -3371,7 +3388,7 @@
       <c r="C64" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" t="s">
         <v>130</v>
       </c>
       <c r="F64" t="s">
@@ -3409,7 +3426,7 @@
       <c r="C65" t="s">
         <v>131</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" t="s">
         <v>132</v>
       </c>
       <c r="F65" t="s">
@@ -3447,7 +3464,7 @@
       <c r="C66" t="s">
         <v>131</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" t="s">
         <v>133</v>
       </c>
       <c r="F66" t="s">
@@ -3485,7 +3502,7 @@
       <c r="C67" t="s">
         <v>131</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" t="s">
         <v>134</v>
       </c>
       <c r="F67" t="s">
@@ -3523,7 +3540,7 @@
       <c r="C68" t="s">
         <v>131</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" t="s">
         <v>135</v>
       </c>
       <c r="F68" t="s">
@@ -3561,7 +3578,7 @@
       <c r="C69" t="s">
         <v>136</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" t="s">
         <v>123</v>
       </c>
       <c r="F69" t="s">
@@ -3599,7 +3616,7 @@
       <c r="C70" t="s">
         <v>136</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" t="s">
         <v>114</v>
       </c>
       <c r="F70" t="s">
@@ -3637,7 +3654,7 @@
       <c r="C71" t="s">
         <v>137</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D71" t="s">
         <v>138</v>
       </c>
       <c r="F71" t="s">
@@ -3675,7 +3692,7 @@
       <c r="C72" t="s">
         <v>137</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D72" t="s">
         <v>139</v>
       </c>
       <c r="F72" t="s">
@@ -3713,7 +3730,7 @@
       <c r="C73" t="s">
         <v>137</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D73" t="s">
         <v>140</v>
       </c>
       <c r="F73" t="s">
@@ -3751,7 +3768,7 @@
       <c r="C74" t="s">
         <v>137</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" t="s">
         <v>138</v>
       </c>
       <c r="F74" t="s">
@@ -3776,6 +3793,158 @@
         <v>18</v>
       </c>
       <c r="M74" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" t="s">
+        <v>142</v>
+      </c>
+      <c r="D75" t="s">
+        <v>143</v>
+      </c>
+      <c r="F75" t="s">
+        <v>42</v>
+      </c>
+      <c r="G75" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" t="s">
+        <v>61</v>
+      </c>
+      <c r="J75" t="s">
+        <v>24</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75" t="s">
+        <v>18</v>
+      </c>
+      <c r="M75" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>33</v>
+      </c>
+      <c r="B76" t="s">
+        <v>141</v>
+      </c>
+      <c r="C76" t="s">
+        <v>142</v>
+      </c>
+      <c r="D76" t="s">
+        <v>144</v>
+      </c>
+      <c r="F76" t="s">
+        <v>42</v>
+      </c>
+      <c r="G76" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" t="s">
+        <v>61</v>
+      </c>
+      <c r="J76" t="s">
+        <v>24</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
+      <c r="L76" t="s">
+        <v>18</v>
+      </c>
+      <c r="M76" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>33</v>
+      </c>
+      <c r="B77" t="s">
+        <v>141</v>
+      </c>
+      <c r="C77" t="s">
+        <v>142</v>
+      </c>
+      <c r="D77" t="s">
+        <v>145</v>
+      </c>
+      <c r="F77" t="s">
+        <v>42</v>
+      </c>
+      <c r="G77" t="s">
+        <v>22</v>
+      </c>
+      <c r="H77" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" t="s">
+        <v>61</v>
+      </c>
+      <c r="J77" t="s">
+        <v>24</v>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" t="s">
+        <v>18</v>
+      </c>
+      <c r="M77" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>33</v>
+      </c>
+      <c r="B78" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" t="s">
+        <v>142</v>
+      </c>
+      <c r="D78" t="s">
+        <v>146</v>
+      </c>
+      <c r="F78" t="s">
+        <v>42</v>
+      </c>
+      <c r="G78" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" t="s">
+        <v>61</v>
+      </c>
+      <c r="J78" t="s">
+        <v>24</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" t="s">
+        <v>18</v>
+      </c>
+      <c r="M78" t="s">
         <v>32</v>
       </c>
     </row>

--- a/keel_trb_smart_template.xlsx
+++ b/keel_trb_smart_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883AF90D-6AD6-4198-A23F-B8027F3405A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7B2821-D06A-4F1A-81E0-5ADE633A402F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,9 +18,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="147">
   <si>
-    <t>Function (Select from List)</t>
-  </si>
-  <si>
     <t>Section / Topic</t>
   </si>
   <si>
@@ -457,6 +454,9 @@
   </si>
   <si>
     <t>Follow the correct procedure for taking over and accepting a watch in port</t>
+  </si>
+  <si>
+    <t>Function</t>
   </si>
 </sst>
 </file>
@@ -869,3083 +869,3083 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
         <v>57</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>58</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>59</v>
       </c>
-      <c r="E2" t="s">
-        <v>60</v>
-      </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
-        <v>58</v>
-      </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
         <v>57</v>
       </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" t="s">
-        <v>58</v>
-      </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
         <v>57</v>
       </c>
-      <c r="C6" t="s">
-        <v>58</v>
-      </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
         <v>57</v>
       </c>
-      <c r="C7" t="s">
-        <v>58</v>
-      </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s">
         <v>57</v>
       </c>
-      <c r="C8" t="s">
-        <v>58</v>
-      </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
         <v>57</v>
       </c>
-      <c r="C9" t="s">
-        <v>58</v>
-      </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
         <v>57</v>
       </c>
-      <c r="C10" t="s">
-        <v>58</v>
-      </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
         <v>57</v>
       </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
         <v>57</v>
       </c>
-      <c r="C12" t="s">
-        <v>58</v>
-      </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
         <v>57</v>
       </c>
-      <c r="C13" t="s">
-        <v>58</v>
-      </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
         <v>57</v>
       </c>
-      <c r="C14" t="s">
-        <v>58</v>
-      </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
         <v>57</v>
       </c>
-      <c r="C15" t="s">
-        <v>58</v>
-      </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
         <v>57</v>
       </c>
-      <c r="C16" t="s">
-        <v>58</v>
-      </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
         <v>57</v>
       </c>
-      <c r="C17" t="s">
-        <v>58</v>
-      </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
         <v>57</v>
       </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
         <v>57</v>
       </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
         <v>57</v>
       </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
         <v>57</v>
       </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
         <v>57</v>
       </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
         <v>57</v>
       </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
         <v>57</v>
       </c>
-      <c r="C24" t="s">
-        <v>58</v>
-      </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" t="s">
         <v>57</v>
       </c>
-      <c r="C25" t="s">
-        <v>58</v>
-      </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
         <v>57</v>
       </c>
-      <c r="C26" t="s">
-        <v>58</v>
-      </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
         <v>57</v>
       </c>
-      <c r="C27" t="s">
-        <v>58</v>
-      </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
         <v>57</v>
       </c>
-      <c r="C28" t="s">
-        <v>58</v>
-      </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
-        <v>58</v>
-      </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
         <v>57</v>
       </c>
-      <c r="C30" t="s">
-        <v>58</v>
-      </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" t="s">
         <v>57</v>
       </c>
-      <c r="C31" t="s">
-        <v>58</v>
-      </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
         <v>57</v>
       </c>
-      <c r="C32" t="s">
-        <v>58</v>
-      </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" t="s">
         <v>57</v>
       </c>
-      <c r="C33" t="s">
-        <v>58</v>
-      </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s">
         <v>57</v>
       </c>
-      <c r="C34" t="s">
-        <v>58</v>
-      </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" t="s">
         <v>57</v>
       </c>
-      <c r="C35" t="s">
-        <v>58</v>
-      </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" t="s">
         <v>57</v>
       </c>
-      <c r="C36" t="s">
-        <v>58</v>
-      </c>
       <c r="D36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" t="s">
         <v>57</v>
       </c>
-      <c r="C37" t="s">
-        <v>58</v>
-      </c>
       <c r="D37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s">
         <v>57</v>
       </c>
-      <c r="C38" t="s">
-        <v>58</v>
-      </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
         <v>57</v>
       </c>
-      <c r="C39" t="s">
-        <v>58</v>
-      </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" t="s">
         <v>99</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>100</v>
       </c>
-      <c r="D40" t="s">
-        <v>101</v>
-      </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J40" t="s">
+        <v>23</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
         <v>24</v>
       </c>
-      <c r="K40" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" t="s">
-        <v>25</v>
-      </c>
       <c r="M40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" t="s">
         <v>99</v>
       </c>
-      <c r="C41" t="s">
-        <v>100</v>
-      </c>
       <c r="D41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J41" t="s">
+        <v>23</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="s">
         <v>24</v>
       </c>
-      <c r="K41" t="b">
-        <v>1</v>
-      </c>
-      <c r="L41" t="s">
-        <v>25</v>
-      </c>
       <c r="M41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" t="s">
         <v>99</v>
       </c>
-      <c r="C42" t="s">
-        <v>100</v>
-      </c>
       <c r="D42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J42" t="s">
+        <v>23</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="s">
         <v>24</v>
       </c>
-      <c r="K42" t="b">
-        <v>1</v>
-      </c>
-      <c r="L42" t="s">
-        <v>25</v>
-      </c>
       <c r="M42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" t="s">
         <v>99</v>
       </c>
-      <c r="C43" t="s">
-        <v>100</v>
-      </c>
       <c r="D43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J43" t="s">
+        <v>23</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="s">
         <v>24</v>
       </c>
-      <c r="K43" t="b">
-        <v>1</v>
-      </c>
-      <c r="L43" t="s">
-        <v>25</v>
-      </c>
       <c r="M43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" t="s">
         <v>99</v>
       </c>
-      <c r="C44" t="s">
-        <v>100</v>
-      </c>
       <c r="D44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J44" t="s">
+        <v>23</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="s">
         <v>24</v>
       </c>
-      <c r="K44" t="b">
-        <v>1</v>
-      </c>
-      <c r="L44" t="s">
-        <v>25</v>
-      </c>
       <c r="M44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" t="s">
         <v>99</v>
       </c>
-      <c r="C45" t="s">
-        <v>100</v>
-      </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J45" t="s">
+        <v>23</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="s">
         <v>24</v>
       </c>
-      <c r="K45" t="b">
-        <v>1</v>
-      </c>
-      <c r="L45" t="s">
-        <v>25</v>
-      </c>
       <c r="M45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" t="s">
         <v>99</v>
       </c>
-      <c r="C46" t="s">
-        <v>100</v>
-      </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J46" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="s">
         <v>24</v>
       </c>
-      <c r="K46" t="b">
-        <v>1</v>
-      </c>
-      <c r="L46" t="s">
-        <v>25</v>
-      </c>
       <c r="M46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" t="s">
         <v>108</v>
       </c>
-      <c r="D47" t="s">
-        <v>109</v>
-      </c>
       <c r="F47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D52" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
       </c>
       <c r="L52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
       </c>
       <c r="L53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C54" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K54" t="b">
         <v>1</v>
       </c>
       <c r="L54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C55" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" t="s">
         <v>116</v>
       </c>
-      <c r="D55" t="s">
-        <v>117</v>
-      </c>
       <c r="F55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K55" t="b">
         <v>1</v>
       </c>
       <c r="L55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D56" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K56" t="b">
         <v>1</v>
       </c>
       <c r="L56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K57" t="b">
         <v>1</v>
       </c>
       <c r="L57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D58" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K58" t="b">
         <v>1</v>
       </c>
       <c r="L58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K59" t="b">
         <v>1</v>
       </c>
       <c r="L59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60" t="s">
         <v>125</v>
       </c>
-      <c r="D60" t="s">
-        <v>126</v>
-      </c>
       <c r="F60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K60" t="b">
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C61" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K61" t="b">
         <v>1</v>
       </c>
       <c r="L61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K62" t="b">
         <v>1</v>
       </c>
       <c r="L62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K63" t="b">
         <v>1</v>
       </c>
       <c r="L63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K64" t="b">
         <v>1</v>
       </c>
       <c r="L64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C65" t="s">
+        <v>130</v>
+      </c>
+      <c r="D65" t="s">
         <v>131</v>
       </c>
-      <c r="D65" t="s">
-        <v>132</v>
-      </c>
       <c r="F65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K65" t="b">
         <v>1</v>
       </c>
       <c r="L65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C66" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K66" t="b">
         <v>1</v>
       </c>
       <c r="L66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M66" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C67" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D67" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I67" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K67" t="b">
         <v>1</v>
       </c>
       <c r="L67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K68" t="b">
         <v>1</v>
       </c>
       <c r="L68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C69" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D69" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K69" t="b">
         <v>1</v>
       </c>
       <c r="L69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C70" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I70" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K70" t="b">
         <v>1</v>
       </c>
       <c r="L70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C71" t="s">
+        <v>136</v>
+      </c>
+      <c r="D71" t="s">
         <v>137</v>
       </c>
-      <c r="D71" t="s">
-        <v>138</v>
-      </c>
       <c r="F71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I71" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K71" t="b">
         <v>1</v>
       </c>
       <c r="L71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C72" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K72" t="b">
         <v>1</v>
       </c>
       <c r="L72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I73" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K73" t="b">
         <v>1</v>
       </c>
       <c r="L73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C74" t="s">
+        <v>136</v>
+      </c>
+      <c r="D74" t="s">
         <v>137</v>
       </c>
-      <c r="D74" t="s">
-        <v>138</v>
-      </c>
       <c r="F74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K74" t="b">
         <v>1</v>
       </c>
       <c r="L74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75" t="s">
         <v>141</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>142</v>
       </c>
-      <c r="D75" t="s">
-        <v>143</v>
-      </c>
       <c r="F75" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G75" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75" t="s">
         <v>22</v>
       </c>
-      <c r="H75" t="s">
-        <v>23</v>
-      </c>
       <c r="I75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K75" t="b">
         <v>1</v>
       </c>
       <c r="L75" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
+        <v>140</v>
+      </c>
+      <c r="C76" t="s">
         <v>141</v>
       </c>
-      <c r="C76" t="s">
-        <v>142</v>
-      </c>
       <c r="D76" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G76" t="s">
+        <v>21</v>
+      </c>
+      <c r="H76" t="s">
         <v>22</v>
       </c>
-      <c r="H76" t="s">
-        <v>23</v>
-      </c>
       <c r="I76" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K76" t="b">
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
+        <v>140</v>
+      </c>
+      <c r="C77" t="s">
         <v>141</v>
       </c>
-      <c r="C77" t="s">
-        <v>142</v>
-      </c>
       <c r="D77" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G77" t="s">
+        <v>21</v>
+      </c>
+      <c r="H77" t="s">
         <v>22</v>
       </c>
-      <c r="H77" t="s">
-        <v>23</v>
-      </c>
       <c r="I77" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K77" t="b">
         <v>1</v>
       </c>
       <c r="L77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B78" t="s">
+        <v>140</v>
+      </c>
+      <c r="C78" t="s">
         <v>141</v>
       </c>
-      <c r="C78" t="s">
-        <v>142</v>
-      </c>
       <c r="D78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G78" t="s">
+        <v>21</v>
+      </c>
+      <c r="H78" t="s">
         <v>22</v>
       </c>
-      <c r="H78" t="s">
-        <v>23</v>
-      </c>
       <c r="I78" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K78" t="b">
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -4015,168 +4015,168 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
       <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
         <v>18</v>
-      </c>
-      <c r="G1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>35</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
         <v>41</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E6" t="s">
         <v>42</v>
-      </c>
-      <c r="E6" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/keel_trb_smart_template.xlsx
+++ b/keel_trb_smart_template.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7B2821-D06A-4F1A-81E0-5ADE633A402F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C8F0B4-9E00-44B9-BD0A-48F99154382B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,12 +11,25 @@
     <sheet name="TRB Tasks" sheetId="1" r:id="rId1"/>
     <sheet name="RefData" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2737" uniqueCount="324">
   <si>
     <t>Section / Topic</t>
   </si>
@@ -360,9 +373,6 @@
     <t>Practise tidal calculations</t>
   </si>
   <si>
-    <t>Practise calculat ions for distance, average speed, course made good, set and drift, ETA</t>
-  </si>
-  <si>
     <t>Determine and apply compass error for courses and compass bearings</t>
   </si>
   <si>
@@ -378,9 +388,6 @@
     <t>Practice Amplitudes</t>
   </si>
   <si>
-    <t>Understand the use of and make ent ries in the compass error book and interpre.t information recorded</t>
-  </si>
-  <si>
     <t>Demonstrate the use of the compass when setting course</t>
   </si>
   <si>
@@ -390,9 +397,6 @@
     <t>Set Courses</t>
   </si>
   <si>
-    <t>Recognise conspicusous objects and other terrestrial/celestial aids to navigation in daylight and at night</t>
-  </si>
-  <si>
     <t>Perform look-out duties and report objects in degrees or points</t>
   </si>
   <si>
@@ -405,9 +409,6 @@
     <t>Practice compass bearings and visual fixes</t>
   </si>
   <si>
-    <t>Demostrate a knowledge of the IALA system of buoyage</t>
-  </si>
-  <si>
     <t>Use azimuth mirror and sextant to fix ship's position by celestial and terrestrial observations</t>
   </si>
   <si>
@@ -457,6 +458,551 @@
   </si>
   <si>
     <t>Function</t>
+  </si>
+  <si>
+    <t>Conduct the watch</t>
+  </si>
+  <si>
+    <t>Assist with the duties of an Engineer Officer during Seagoing watches</t>
+  </si>
+  <si>
+    <t>Assist with the duties of an Engineer Officer during Port watches</t>
+  </si>
+  <si>
+    <t>Assist with the duties of an Engineer Officer during Anchor watches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under supervision, carry out all routine watchkeeping duties, check the correct functioning of all automatic control and monitoring systems. </t>
+  </si>
+  <si>
+    <t>Under supervision, carry out all routine watchkeeping duties, make adjustments as found necessary for the correct functioning of all automatic control and monitoring systems.</t>
+  </si>
+  <si>
+    <t>Perform routine checks in machinery space for correct water levels</t>
+  </si>
+  <si>
+    <t>Blow down the main engine scavenge drains</t>
+  </si>
+  <si>
+    <t>Ensure that compressed air automatic drains are functioning correctly</t>
+  </si>
+  <si>
+    <t>Clean air side of turbo charger</t>
+  </si>
+  <si>
+    <t>Carry out boiler water tests and corrective treatment</t>
+  </si>
+  <si>
+    <t>Check returns from heating coils and other possible sources of contaminated feedwater</t>
+  </si>
+  <si>
+    <t>Check the correct operation of the boiler Including water level and burner</t>
+  </si>
+  <si>
+    <t>Carry out a soot-blowing procedure</t>
+  </si>
+  <si>
+    <t>Check all air receiver drains</t>
+  </si>
+  <si>
+    <t>Assist on the bridge during manoeuvring operations while entering port</t>
+  </si>
+  <si>
+    <t>Assist on the bridge during manoeuvring operations while leaving port</t>
+  </si>
+  <si>
+    <t>Response to black-out and emergency situations</t>
+  </si>
+  <si>
+    <t>Take corrective action during emergency Fire Drill</t>
+  </si>
+  <si>
+    <t>Take corrective action during emergency Blackout Drill</t>
+  </si>
+  <si>
+    <t>Take corrective action during emergency Enclosed Space Rescue Drill</t>
+  </si>
+  <si>
+    <t>Assist with/demonstrate use of main engine local control and emergency manoeuvring</t>
+  </si>
+  <si>
+    <t>Assist with/demonstrate procedure for returning main engine to normal running</t>
+  </si>
+  <si>
+    <t>Demonstrate in a drill, emergency running and manoeuvring procedures</t>
+  </si>
+  <si>
+    <t>Demonstrate knowledge of emergency steering gear operation</t>
+  </si>
+  <si>
+    <t>State the priorities for restoring services</t>
+  </si>
+  <si>
+    <t>Change-over of remote-automatic and local control systems</t>
+  </si>
+  <si>
+    <t>Change over to the stand by system for Main engines</t>
+  </si>
+  <si>
+    <t>Change over to the stand by system for Auxiliary engines</t>
+  </si>
+  <si>
+    <t>Change over to the stand by system for Main engine system pumps</t>
+  </si>
+  <si>
+    <t>Change over to the stand by system for Steering Gear</t>
+  </si>
+  <si>
+    <t>Prepare for stand by engines</t>
+  </si>
+  <si>
+    <t>Complete the engine room log book and record books</t>
+  </si>
+  <si>
+    <t>Record the complete engine movements in the log during periods of manoeuvring</t>
+  </si>
+  <si>
+    <t>Evaluate record entries in the Alarm Record Book</t>
+  </si>
+  <si>
+    <t>Observe and note performance and condition of machinery using condition monitoring equipment, where appropriate</t>
+  </si>
+  <si>
+    <t>Observe and note normal operating temperatures/
+pressures</t>
+  </si>
+  <si>
+    <t>Complete the engine room log book and other record books</t>
+  </si>
+  <si>
+    <t>Knowledge of engine room resource management principles</t>
+  </si>
+  <si>
+    <t>Understand that to achieve a goal or an objective the plan must be specific with sufficient detail</t>
+  </si>
+  <si>
+    <t>Demonstrate collection and interpretation of management data to assess task progress</t>
+  </si>
+  <si>
+    <t>lead task review on completion giving credit where due and noting areas where things may be done differently on another occasion</t>
+  </si>
+  <si>
+    <t>Use English in written and oral form</t>
+  </si>
+  <si>
+    <t>Use English engineering publications, operational manuals and fault finding instructions</t>
+  </si>
+  <si>
+    <t>List English language publications or manuals used:</t>
+  </si>
+  <si>
+    <t>If appropriate, assist with completion of ship's Planned Maintenance System records in English</t>
+  </si>
+  <si>
+    <t>Communicate with other in English language, as appropriate</t>
+  </si>
+  <si>
+    <t>Demonstrate correct use of terms used in the engine room and names of machinery, equipment and tools</t>
+  </si>
+  <si>
+    <t>Give and take orders in English during Routine Operations</t>
+  </si>
+  <si>
+    <t>Give and take orders in English during Emergency Drills</t>
+  </si>
+  <si>
+    <t>Ensure that others have understood orders correctly</t>
+  </si>
+  <si>
+    <t>Demonstrate an ability to communicate instructions effectively in the English language to a multi-lingual crew</t>
+  </si>
+  <si>
+    <t>Use Internal communication systems</t>
+  </si>
+  <si>
+    <t>Operation of all internal communication systems on board</t>
+  </si>
+  <si>
+    <t>Demonstrate operation of the ship's internal phone system</t>
+  </si>
+  <si>
+    <t>Use internal message system to send and receive information or instructions</t>
+  </si>
+  <si>
+    <t>Understand communication is a two-way exchange and demonstrate this in practice during steering gear to engine room communication</t>
+  </si>
+  <si>
+    <t>Understand communication is a two-way exchange and demonstrate this in practice during steering gear to bridge communication</t>
+  </si>
+  <si>
+    <t>Understand communication is a two-way exchange and demonstrate this in practice during engine room to bridge communication</t>
+  </si>
+  <si>
+    <t>Demonstrate a knowledge of how to reset machinery following failure and how to restart plant</t>
+  </si>
+  <si>
+    <t>Demonstrate knowledge of first start arrangements</t>
+  </si>
+  <si>
+    <t>Set realistic plans for allocation and use of engine room
+resources</t>
+  </si>
+  <si>
+    <t>Plan tasks to achieve timely outcome</t>
+  </si>
+  <si>
+    <t>Lead progress review with team members to ensure task is attainable within the plan set</t>
+  </si>
+  <si>
+    <t>Practise calculations for distance, average speed, course made good, set and drift, ETA</t>
+  </si>
+  <si>
+    <t>Understand the use of and make entries in the compass error book and interpret information recorded</t>
+  </si>
+  <si>
+    <t>Recognise conspicuous objects and other terrestrial/celestial aids to navigation in daylight and at night</t>
+  </si>
+  <si>
+    <t>Demonstrate a knowledge of the IALA system of buoyage</t>
+  </si>
+  <si>
+    <t>Check sheathing on high-pressure fuel pipes</t>
+  </si>
+  <si>
+    <t>Understand that effective watchkeeping involves managing watch duties, including supervision, as well as maintaining the safe operation of propulsion plant and other machinery</t>
+  </si>
+  <si>
+    <t>Take corrective action during emergency Abandon ship Drill</t>
+  </si>
+  <si>
+    <t>Demonstrate acknowledge of and understand the purpose of the Alarm Record Book</t>
+  </si>
+  <si>
+    <t>Demonstrate correct station ID procedure when using hand held transceivers (portable radios)</t>
+  </si>
+  <si>
+    <t>Complete records accurately and in a timely way when recording information received by telephone or hand held transceivers (portable radios)</t>
+  </si>
+  <si>
+    <t>Operate main and auxiliary machinery and associated control systems</t>
+  </si>
+  <si>
+    <t>Prepare machinery for departure from port</t>
+  </si>
+  <si>
+    <t>Draw a schematic arrangement of  the main engine system, using blocks to Indicate the main components</t>
+  </si>
+  <si>
+    <t>Confirm bridge and ER communications</t>
+  </si>
+  <si>
+    <t>Check starting air compressor and prepare starting air system</t>
+  </si>
+  <si>
+    <t>Prepare main and auxiliary machinery for port departure</t>
+  </si>
+  <si>
+    <t>Prepare main and auxiliary machinery for the sea passage</t>
+  </si>
+  <si>
+    <t>Prepare and test the steering gear and telegraphs</t>
+  </si>
+  <si>
+    <t>Demonstrate a knowledge of the use of high level and low level sea suctions</t>
+  </si>
+  <si>
+    <t>All checks and actions are carried out in accordance with laid down instructions and all auxiliary and control systems are functioning properly. All relevant checks and actions are recorded.</t>
+  </si>
+  <si>
+    <t>Transmission and reception of messages are consistently successful. Communication records must be complete, accurate and comply with statutory requirements.</t>
+  </si>
+  <si>
+    <t>Operate main and auxiliary machinery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sketch, in diagramatic form, the main systems for Auxiliary engine for your ship. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sketch, in diagramatic form, the main systems for boiler system for your ship. </t>
+  </si>
+  <si>
+    <t>Start the main engine from local and remote control positions</t>
+  </si>
+  <si>
+    <t>Carry out post start-up checks of main engine and shafting</t>
+  </si>
+  <si>
+    <t>Manually operate main compressor and change over to normal automatic running mode</t>
+  </si>
+  <si>
+    <t>The machinery must be operated in accordance with instructions, procedures and safe working practices. All instruments are monitored, necessary adjustments made and required actions carried out and properly recorded</t>
+  </si>
+  <si>
+    <t>Water wash exhaust side main engine turbocharger</t>
+  </si>
+  <si>
+    <t>Prepare for running and operate an evaporator/fresh water generator</t>
+  </si>
+  <si>
+    <t>Apply tests and conditioning for purity and potability of fresh water</t>
+  </si>
+  <si>
+    <t>Check governors</t>
+  </si>
+  <si>
+    <t>Record pressures and temperatures for normal running, and note system valve settings and positions in normal running mode</t>
+  </si>
+  <si>
+    <t>Respond to instructions from the bridge and operate the main engine controls during periods of manoeuvring</t>
+  </si>
+  <si>
+    <t>Change local/manual control of machinery and systems to remote/automatic control as appropriate</t>
+  </si>
+  <si>
+    <t>Adjust main engine and auxiliary machinery for  continuous running</t>
+  </si>
+  <si>
+    <t>Report abnormal conditions, making a record of same and note corrective action required</t>
+  </si>
+  <si>
+    <t>Check crankcase oil mist detector and demonstrate action to be taken in case of  an alarm</t>
+  </si>
+  <si>
+    <t>Take power diagram or readings and calculate mean effective pressure and indicated power</t>
+  </si>
+  <si>
+    <t>Carry out  routine tests on Engine cooling water</t>
+  </si>
+  <si>
+    <t>Carry out  routine tests on Fuel oil</t>
+  </si>
+  <si>
+    <t>Carry out  routine tests on Lube oil</t>
+  </si>
+  <si>
+    <t>Assist with shutting down main engine and auxiliary systems after finishing with engines</t>
+  </si>
+  <si>
+    <t>Fill a boiler and raise steam from cold</t>
+  </si>
+  <si>
+    <t>Raise the  temperature of main engine fuel oil from cold to the correct level</t>
+  </si>
+  <si>
+    <t>Admit steam to a line or system, taking all precautions against thermal and pressure shock and avoiding water hammer effect</t>
+  </si>
+  <si>
+    <t>Check the security of steam pipes and any expansion pieces</t>
+  </si>
+  <si>
+    <t>Check that steam traps and drains are functioning</t>
+  </si>
+  <si>
+    <t>Close down a steam line, observing procedure for draining</t>
+  </si>
+  <si>
+    <t>Check quality of combustion, noting Smoke from the funnel, Clarity around the flame, Flame shape, size and colour, Excess air, CO/CO reading, Carbon and unburnt fuel deposits</t>
+  </si>
+  <si>
+    <t>Check the correct functioning of all boiler condition indicators and alarms</t>
+  </si>
+  <si>
+    <t>Check that correct boiler water level Is maintained</t>
+  </si>
+  <si>
+    <t>Demonstrate the correct procedure for blowing down a boiler gauge glass</t>
+  </si>
+  <si>
+    <t>Explain the effect of varying the temperature of circulating water</t>
+  </si>
+  <si>
+    <t>Start up and operate ship's refrigeration plant</t>
+  </si>
+  <si>
+    <t>Make up brine, if appropriate</t>
+  </si>
+  <si>
+    <t>Check density of the brine</t>
+  </si>
+  <si>
+    <t>Shut down and secure refrigeration/AC plant</t>
+  </si>
+  <si>
+    <t>Carry out refrigerant charging procedure</t>
+  </si>
+  <si>
+    <t>Carry out leak detection for refrigerant gases</t>
+  </si>
+  <si>
+    <t>Replenish driers arid f ilters</t>
+  </si>
+  <si>
+    <t>Check pressure tank safety devices</t>
+  </si>
+  <si>
+    <t>Put sewage system on line and check correct operation</t>
+  </si>
+  <si>
+    <t>Operate Incinerator</t>
+  </si>
+  <si>
+    <t>Operate Shredder/Compator</t>
+  </si>
+  <si>
+    <t>Operate fuel, lubrication, ballast and other pumping systems and associated control systems</t>
+  </si>
+  <si>
+    <t>Plan the operations of auxiliary and piping systems and service plants</t>
+  </si>
+  <si>
+    <t>Sketch a line diagram of the oily water separator (OWS) system</t>
+  </si>
+  <si>
+    <t>Demonstrate a knowledge of making correct entries in the Oil Record Book</t>
+  </si>
+  <si>
+    <t>Sketch a line diagram of the ballast water system</t>
+  </si>
+  <si>
+    <t>Sketch a line diagram of the engine room bilge water system</t>
+  </si>
+  <si>
+    <t>Sketch a line diagram of the hold bilge water system</t>
+  </si>
+  <si>
+    <t>Assist with the operation of the OWS</t>
+  </si>
+  <si>
+    <t>Assist with planning ballast water management operations</t>
+  </si>
+  <si>
+    <t>Plan and line-up the Ballast water pump</t>
+  </si>
+  <si>
+    <t>Plan and line-up the BIige pump</t>
+  </si>
+  <si>
+    <t>Demonstrate a knowledge of the bilge pump</t>
+  </si>
+  <si>
+    <t>Sketch a line diagram of the fuel oil bunker system</t>
+  </si>
+  <si>
+    <t>Assist with planning for receiving bunkers</t>
+  </si>
+  <si>
+    <t>Assist with planning for transfer of fuel from bunker tanks to service tanks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations must be planned and all equipment and control systems should be checked before operations are executed. </t>
+  </si>
+  <si>
+    <t>Operate the systems for fuel oil, lube oil, ballast, bilge, MARPOL equipment and cargo pumping</t>
+  </si>
+  <si>
+    <t>Under supervision, transfer fuel from bunkers to service  tanks, observing all safety, ship stability and pollution prevention requirements</t>
+  </si>
+  <si>
+    <t>Drain water/sludge from settling tanks</t>
+  </si>
+  <si>
+    <t>Start, operate and monitor fuel oil purifiers</t>
+  </si>
+  <si>
+    <t>Demonstrate a knowledge of Sulphur Emissions Control Areas</t>
+  </si>
+  <si>
+    <t>Assist an officer with change over from heavy fuel oil to low viscosity fuel oil and vice versa, where applicable</t>
+  </si>
+  <si>
+    <t>Start, operate and monitor lube oil purifiers</t>
+  </si>
+  <si>
+    <t>Perform routine checks and top ups to maintain lube oil system tanks at the correct levels</t>
+  </si>
+  <si>
+    <t>Assist with loading and discharging cargo tanks, including stripping procedures</t>
+  </si>
+  <si>
+    <t>Set up and use an OWS In compliance with MARPOL</t>
+  </si>
+  <si>
+    <t>Operate an oil discharge monitor in compliance with MARPOL (oil tankers)</t>
+  </si>
+  <si>
+    <t>Use bilge holding tanks</t>
+  </si>
+  <si>
+    <t>Observe all pollution prevention requirements</t>
+  </si>
+  <si>
+    <t>Open up OWS units, clean all parts and reassemble</t>
+  </si>
+  <si>
+    <t>Observing all safety, ship stability and pollution prevention requirements, assist an officer with ballasting</t>
+  </si>
+  <si>
+    <t>Observing all safety, ship stability and pollution prevention requirements, assist an officer with deballasting</t>
+  </si>
+  <si>
+    <t>Pump out hold bilges ensuring that all pollution prevention regulations and requirements are observed</t>
+  </si>
+  <si>
+    <t>Demonstrate the emergency arrangements for emptying engine room bilges in the event of flooding</t>
+  </si>
+  <si>
+    <t>The operations must be carried out in accordance with rules and procedures to ensure safety of operations and avoid pollution of the marine environment</t>
+  </si>
+  <si>
+    <t>Operate electrical, electronic and control systems</t>
+  </si>
+  <si>
+    <t>Basic configuration and operating principles of electrical equipment</t>
+  </si>
+  <si>
+    <t>Explain the difference between a system diagram, a circuit diagram and a wiring diagram</t>
+  </si>
+  <si>
+    <t>The instructions and manuals relevant for safe and efficient operations should be quickly identified and properly used. Electrical systems must be understood and explained with drawings/instructions</t>
+  </si>
+  <si>
+    <t>Demonstrate an ability to use ship's diagrams to identify Main circuit breakers</t>
+  </si>
+  <si>
+    <t>Demonstrate an ability to use ship's diagrams to identify Emergency switchboard connections</t>
+  </si>
+  <si>
+    <t>Demonstrate an ability to use ship's diagrams to identify Trips (over current, reverse power, low frequency)</t>
+  </si>
+  <si>
+    <t>Demonstrate an ability to use ship's diagrams to identify Transformers</t>
+  </si>
+  <si>
+    <t>Demonstrate an ability to use ship's diagrams to identify Fuses</t>
+  </si>
+  <si>
+    <t>Demonstrate an ability to use ship's diagrams to identify Supply voltages</t>
+  </si>
+  <si>
+    <t>Demonstrate an ability to use ship's diagrams to identify Shore connections</t>
+  </si>
+  <si>
+    <t>Demonstrate an ability to use ship's diagrams to identify Loads to each piece of equipment</t>
+  </si>
+  <si>
+    <t>Demonstrate an ability to use ship's diagrams to identify The types of motors and motor starters</t>
+  </si>
+  <si>
+    <t>Demonstrate a knowledge of symbols commonly used on circuit diagrams</t>
+  </si>
+  <si>
+    <t>Demonstrate a knowledge of the location of major control and protection devices within the distribution network</t>
+  </si>
+  <si>
+    <t>Demonstrate a knowledge of which electrical loads are classed as essent ial or non-essential, and how essential services are supplied</t>
+  </si>
+  <si>
+    <t>Locate shore power connection and state the procedures for connection/disconnection</t>
   </si>
 </sst>
 </file>
@@ -509,9 +1055,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -851,12 +1398,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M232"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="4" width="40" customWidth="1"/>
+    <col min="3" max="3" width="54.140625" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -869,7 +1417,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2816,10 +3364,10 @@
         <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D49" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F49" t="s">
         <v>13</v>
@@ -2854,7 +3402,7 @@
         <v>98</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D50" t="s">
         <v>110</v>
@@ -2892,7 +3440,7 @@
         <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D51" t="s">
         <v>111</v>
@@ -2930,10 +3478,10 @@
         <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D52" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F52" t="s">
         <v>13</v>
@@ -2968,7 +3516,7 @@
         <v>98</v>
       </c>
       <c r="C53" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D53" t="s">
         <v>113</v>
@@ -3009,7 +3557,7 @@
         <v>112</v>
       </c>
       <c r="D54" t="s">
-        <v>114</v>
+        <v>207</v>
       </c>
       <c r="F54" t="s">
         <v>13</v>
@@ -3044,10 +3592,10 @@
         <v>98</v>
       </c>
       <c r="C55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" t="s">
         <v>115</v>
-      </c>
-      <c r="D55" t="s">
-        <v>116</v>
       </c>
       <c r="F55" t="s">
         <v>13</v>
@@ -3082,10 +3630,10 @@
         <v>98</v>
       </c>
       <c r="C56" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F56" t="s">
         <v>13</v>
@@ -3120,10 +3668,10 @@
         <v>98</v>
       </c>
       <c r="C57" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F57" t="s">
         <v>13</v>
@@ -3158,10 +3706,10 @@
         <v>98</v>
       </c>
       <c r="C58" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F58" t="s">
         <v>13</v>
@@ -3196,10 +3744,10 @@
         <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D59" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
       <c r="F59" t="s">
         <v>13</v>
@@ -3234,10 +3782,10 @@
         <v>98</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="D60" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
@@ -3272,10 +3820,10 @@
         <v>98</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F61" t="s">
         <v>13</v>
@@ -3310,10 +3858,10 @@
         <v>98</v>
       </c>
       <c r="C62" t="s">
+        <v>209</v>
+      </c>
+      <c r="D62" t="s">
         <v>124</v>
-      </c>
-      <c r="D62" t="s">
-        <v>127</v>
       </c>
       <c r="F62" t="s">
         <v>13</v>
@@ -3348,10 +3896,10 @@
         <v>98</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="D63" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F63" t="s">
         <v>13</v>
@@ -3386,10 +3934,10 @@
         <v>98</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="D64" t="s">
-        <v>129</v>
+        <v>210</v>
       </c>
       <c r="F64" t="s">
         <v>13</v>
@@ -3424,10 +3972,10 @@
         <v>98</v>
       </c>
       <c r="C65" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D65" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
@@ -3462,10 +4010,10 @@
         <v>98</v>
       </c>
       <c r="C66" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D66" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>
@@ -3500,10 +4048,10 @@
         <v>98</v>
       </c>
       <c r="C67" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D67" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F67" t="s">
         <v>13</v>
@@ -3538,10 +4086,10 @@
         <v>98</v>
       </c>
       <c r="C68" t="s">
+        <v>126</v>
+      </c>
+      <c r="D68" t="s">
         <v>130</v>
-      </c>
-      <c r="D68" t="s">
-        <v>134</v>
       </c>
       <c r="F68" t="s">
         <v>13</v>
@@ -3576,10 +4124,10 @@
         <v>98</v>
       </c>
       <c r="C69" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D69" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
@@ -3614,7 +4162,7 @@
         <v>98</v>
       </c>
       <c r="C70" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D70" t="s">
         <v>113</v>
@@ -3652,10 +4200,10 @@
         <v>98</v>
       </c>
       <c r="C71" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D71" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F71" t="s">
         <v>13</v>
@@ -3690,10 +4238,10 @@
         <v>98</v>
       </c>
       <c r="C72" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D72" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F72" t="s">
         <v>13</v>
@@ -3728,10 +4276,10 @@
         <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D73" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F73" t="s">
         <v>13</v>
@@ -3766,10 +4314,10 @@
         <v>98</v>
       </c>
       <c r="C74" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D74" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F74" t="s">
         <v>13</v>
@@ -3801,13 +4349,13 @@
         <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C75" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D75" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F75" t="s">
         <v>41</v>
@@ -3839,13 +4387,13 @@
         <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C76" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D76" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F76" t="s">
         <v>41</v>
@@ -3877,13 +4425,13 @@
         <v>32</v>
       </c>
       <c r="B77" t="s">
+        <v>136</v>
+      </c>
+      <c r="C77" t="s">
+        <v>137</v>
+      </c>
+      <c r="D77" t="s">
         <v>140</v>
-      </c>
-      <c r="C77" t="s">
-        <v>141</v>
-      </c>
-      <c r="D77" t="s">
-        <v>144</v>
       </c>
       <c r="F77" t="s">
         <v>41</v>
@@ -3915,43 +4463,6198 @@
         <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C78" t="s">
+        <v>137</v>
+      </c>
+      <c r="D78" t="s">
         <v>141</v>
       </c>
-      <c r="D78" t="s">
+      <c r="F78" t="s">
+        <v>41</v>
+      </c>
+      <c r="G78" t="s">
+        <v>21</v>
+      </c>
+      <c r="H78" t="s">
+        <v>22</v>
+      </c>
+      <c r="I78" t="s">
+        <v>60</v>
+      </c>
+      <c r="J78" t="s">
+        <v>23</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" t="s">
+        <v>17</v>
+      </c>
+      <c r="M78" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>32</v>
+      </c>
+      <c r="B79" t="s">
+        <v>136</v>
+      </c>
+      <c r="C79" t="s">
+        <v>143</v>
+      </c>
+      <c r="D79" t="s">
+        <v>144</v>
+      </c>
+      <c r="F79" t="s">
+        <v>41</v>
+      </c>
+      <c r="G79" t="s">
+        <v>21</v>
+      </c>
+      <c r="H79" t="s">
+        <v>22</v>
+      </c>
+      <c r="I79" t="s">
+        <v>60</v>
+      </c>
+      <c r="J79" t="s">
+        <v>23</v>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L79" t="s">
+        <v>17</v>
+      </c>
+      <c r="M79" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>32</v>
+      </c>
+      <c r="B80" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80" t="s">
+        <v>143</v>
+      </c>
+      <c r="D80" t="s">
         <v>145</v>
       </c>
-      <c r="F78" t="s">
-        <v>41</v>
-      </c>
-      <c r="G78" t="s">
-        <v>21</v>
-      </c>
-      <c r="H78" t="s">
-        <v>22</v>
-      </c>
-      <c r="I78" t="s">
-        <v>60</v>
-      </c>
-      <c r="J78" t="s">
-        <v>23</v>
-      </c>
-      <c r="K78" t="b">
-        <v>1</v>
-      </c>
-      <c r="L78" t="s">
-        <v>17</v>
-      </c>
-      <c r="M78" t="s">
+      <c r="F80" t="s">
+        <v>41</v>
+      </c>
+      <c r="G80" t="s">
+        <v>21</v>
+      </c>
+      <c r="H80" t="s">
+        <v>22</v>
+      </c>
+      <c r="I80" t="s">
+        <v>60</v>
+      </c>
+      <c r="J80" t="s">
+        <v>23</v>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" t="s">
+        <v>17</v>
+      </c>
+      <c r="M80" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>32</v>
+      </c>
+      <c r="B81" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81" t="s">
+        <v>143</v>
+      </c>
+      <c r="D81" t="s">
+        <v>146</v>
+      </c>
+      <c r="F81" t="s">
+        <v>41</v>
+      </c>
+      <c r="G81" t="s">
+        <v>21</v>
+      </c>
+      <c r="H81" t="s">
+        <v>22</v>
+      </c>
+      <c r="I81" t="s">
+        <v>60</v>
+      </c>
+      <c r="J81" t="s">
+        <v>23</v>
+      </c>
+      <c r="K81" t="b">
+        <v>1</v>
+      </c>
+      <c r="L81" t="s">
+        <v>17</v>
+      </c>
+      <c r="M81" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>32</v>
+      </c>
+      <c r="B82" t="s">
+        <v>136</v>
+      </c>
+      <c r="C82" t="s">
+        <v>143</v>
+      </c>
+      <c r="D82" t="s">
+        <v>147</v>
+      </c>
+      <c r="F82" t="s">
+        <v>41</v>
+      </c>
+      <c r="G82" t="s">
+        <v>21</v>
+      </c>
+      <c r="H82" t="s">
+        <v>22</v>
+      </c>
+      <c r="I82" t="s">
+        <v>60</v>
+      </c>
+      <c r="J82" t="s">
+        <v>23</v>
+      </c>
+      <c r="K82" t="b">
+        <v>1</v>
+      </c>
+      <c r="L82" t="s">
+        <v>17</v>
+      </c>
+      <c r="M82" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>32</v>
+      </c>
+      <c r="B83" t="s">
+        <v>136</v>
+      </c>
+      <c r="C83" t="s">
+        <v>143</v>
+      </c>
+      <c r="D83" t="s">
+        <v>148</v>
+      </c>
+      <c r="F83" t="s">
+        <v>41</v>
+      </c>
+      <c r="G83" t="s">
+        <v>21</v>
+      </c>
+      <c r="H83" t="s">
+        <v>22</v>
+      </c>
+      <c r="I83" t="s">
+        <v>60</v>
+      </c>
+      <c r="J83" t="s">
+        <v>23</v>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L83" t="s">
+        <v>17</v>
+      </c>
+      <c r="M83" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>32</v>
+      </c>
+      <c r="B84" t="s">
+        <v>136</v>
+      </c>
+      <c r="C84" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84" t="s">
+        <v>149</v>
+      </c>
+      <c r="F84" t="s">
+        <v>41</v>
+      </c>
+      <c r="G84" t="s">
+        <v>21</v>
+      </c>
+      <c r="H84" t="s">
+        <v>22</v>
+      </c>
+      <c r="I84" t="s">
+        <v>60</v>
+      </c>
+      <c r="J84" t="s">
+        <v>23</v>
+      </c>
+      <c r="K84" t="b">
+        <v>1</v>
+      </c>
+      <c r="L84" t="s">
+        <v>17</v>
+      </c>
+      <c r="M84" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>32</v>
+      </c>
+      <c r="B85" t="s">
+        <v>136</v>
+      </c>
+      <c r="C85" t="s">
+        <v>143</v>
+      </c>
+      <c r="D85" t="s">
+        <v>150</v>
+      </c>
+      <c r="F85" t="s">
+        <v>41</v>
+      </c>
+      <c r="G85" t="s">
+        <v>21</v>
+      </c>
+      <c r="H85" t="s">
+        <v>22</v>
+      </c>
+      <c r="I85" t="s">
+        <v>60</v>
+      </c>
+      <c r="J85" t="s">
+        <v>23</v>
+      </c>
+      <c r="K85" t="b">
+        <v>1</v>
+      </c>
+      <c r="L85" t="s">
+        <v>17</v>
+      </c>
+      <c r="M85" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>32</v>
+      </c>
+      <c r="B86" t="s">
+        <v>136</v>
+      </c>
+      <c r="C86" t="s">
+        <v>143</v>
+      </c>
+      <c r="D86" t="s">
+        <v>151</v>
+      </c>
+      <c r="F86" t="s">
+        <v>41</v>
+      </c>
+      <c r="G86" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86" t="s">
+        <v>22</v>
+      </c>
+      <c r="I86" t="s">
+        <v>60</v>
+      </c>
+      <c r="J86" t="s">
+        <v>23</v>
+      </c>
+      <c r="K86" t="b">
+        <v>1</v>
+      </c>
+      <c r="L86" t="s">
+        <v>17</v>
+      </c>
+      <c r="M86" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>32</v>
+      </c>
+      <c r="B87" t="s">
+        <v>136</v>
+      </c>
+      <c r="C87" t="s">
+        <v>143</v>
+      </c>
+      <c r="D87" t="s">
+        <v>211</v>
+      </c>
+      <c r="F87" t="s">
+        <v>41</v>
+      </c>
+      <c r="G87" t="s">
+        <v>21</v>
+      </c>
+      <c r="H87" t="s">
+        <v>22</v>
+      </c>
+      <c r="I87" t="s">
+        <v>60</v>
+      </c>
+      <c r="J87" t="s">
+        <v>23</v>
+      </c>
+      <c r="K87" t="b">
+        <v>1</v>
+      </c>
+      <c r="L87" t="s">
+        <v>17</v>
+      </c>
+      <c r="M87" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>32</v>
+      </c>
+      <c r="B88" t="s">
+        <v>136</v>
+      </c>
+      <c r="C88" t="s">
+        <v>143</v>
+      </c>
+      <c r="D88" t="s">
+        <v>152</v>
+      </c>
+      <c r="F88" t="s">
+        <v>41</v>
+      </c>
+      <c r="G88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H88" t="s">
+        <v>22</v>
+      </c>
+      <c r="I88" t="s">
+        <v>60</v>
+      </c>
+      <c r="J88" t="s">
+        <v>23</v>
+      </c>
+      <c r="K88" t="b">
+        <v>1</v>
+      </c>
+      <c r="L88" t="s">
+        <v>17</v>
+      </c>
+      <c r="M88" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>32</v>
+      </c>
+      <c r="B89" t="s">
+        <v>136</v>
+      </c>
+      <c r="C89" t="s">
+        <v>143</v>
+      </c>
+      <c r="D89" t="s">
+        <v>153</v>
+      </c>
+      <c r="F89" t="s">
+        <v>41</v>
+      </c>
+      <c r="G89" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" t="s">
+        <v>22</v>
+      </c>
+      <c r="I89" t="s">
+        <v>60</v>
+      </c>
+      <c r="J89" t="s">
+        <v>23</v>
+      </c>
+      <c r="K89" t="b">
+        <v>1</v>
+      </c>
+      <c r="L89" t="s">
+        <v>17</v>
+      </c>
+      <c r="M89" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90" t="s">
+        <v>136</v>
+      </c>
+      <c r="C90" t="s">
+        <v>143</v>
+      </c>
+      <c r="D90" t="s">
+        <v>154</v>
+      </c>
+      <c r="F90" t="s">
+        <v>41</v>
+      </c>
+      <c r="G90" t="s">
+        <v>21</v>
+      </c>
+      <c r="H90" t="s">
+        <v>22</v>
+      </c>
+      <c r="I90" t="s">
+        <v>60</v>
+      </c>
+      <c r="J90" t="s">
+        <v>23</v>
+      </c>
+      <c r="K90" t="b">
+        <v>1</v>
+      </c>
+      <c r="L90" t="s">
+        <v>17</v>
+      </c>
+      <c r="M90" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>32</v>
+      </c>
+      <c r="B91" t="s">
+        <v>136</v>
+      </c>
+      <c r="C91" t="s">
+        <v>143</v>
+      </c>
+      <c r="D91" t="s">
+        <v>155</v>
+      </c>
+      <c r="F91" t="s">
+        <v>41</v>
+      </c>
+      <c r="G91" t="s">
+        <v>21</v>
+      </c>
+      <c r="H91" t="s">
+        <v>22</v>
+      </c>
+      <c r="I91" t="s">
+        <v>60</v>
+      </c>
+      <c r="J91" t="s">
+        <v>23</v>
+      </c>
+      <c r="K91" t="b">
+        <v>1</v>
+      </c>
+      <c r="L91" t="s">
+        <v>17</v>
+      </c>
+      <c r="M91" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>32</v>
+      </c>
+      <c r="B92" t="s">
+        <v>136</v>
+      </c>
+      <c r="C92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D92" t="s">
+        <v>156</v>
+      </c>
+      <c r="F92" t="s">
+        <v>41</v>
+      </c>
+      <c r="G92" t="s">
+        <v>21</v>
+      </c>
+      <c r="H92" t="s">
+        <v>22</v>
+      </c>
+      <c r="I92" t="s">
+        <v>60</v>
+      </c>
+      <c r="J92" t="s">
+        <v>23</v>
+      </c>
+      <c r="K92" t="b">
+        <v>1</v>
+      </c>
+      <c r="L92" t="s">
+        <v>17</v>
+      </c>
+      <c r="M92" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>32</v>
+      </c>
+      <c r="B93" t="s">
+        <v>136</v>
+      </c>
+      <c r="C93" t="s">
+        <v>143</v>
+      </c>
+      <c r="D93" t="s">
+        <v>157</v>
+      </c>
+      <c r="F93" t="s">
+        <v>41</v>
+      </c>
+      <c r="G93" t="s">
+        <v>21</v>
+      </c>
+      <c r="H93" t="s">
+        <v>22</v>
+      </c>
+      <c r="I93" t="s">
+        <v>60</v>
+      </c>
+      <c r="J93" t="s">
+        <v>23</v>
+      </c>
+      <c r="K93" t="b">
+        <v>1</v>
+      </c>
+      <c r="L93" t="s">
+        <v>17</v>
+      </c>
+      <c r="M93" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>32</v>
+      </c>
+      <c r="B94" t="s">
+        <v>136</v>
+      </c>
+      <c r="C94" t="s">
+        <v>143</v>
+      </c>
+      <c r="D94" t="s">
+        <v>158</v>
+      </c>
+      <c r="F94" t="s">
+        <v>41</v>
+      </c>
+      <c r="G94" t="s">
+        <v>21</v>
+      </c>
+      <c r="H94" t="s">
+        <v>22</v>
+      </c>
+      <c r="I94" t="s">
+        <v>60</v>
+      </c>
+      <c r="J94" t="s">
+        <v>23</v>
+      </c>
+      <c r="K94" t="b">
+        <v>1</v>
+      </c>
+      <c r="L94" t="s">
+        <v>17</v>
+      </c>
+      <c r="M94" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>32</v>
+      </c>
+      <c r="B95" t="s">
+        <v>136</v>
+      </c>
+      <c r="C95" t="s">
+        <v>143</v>
+      </c>
+      <c r="D95" t="s">
+        <v>159</v>
+      </c>
+      <c r="F95" t="s">
+        <v>41</v>
+      </c>
+      <c r="G95" t="s">
+        <v>21</v>
+      </c>
+      <c r="H95" t="s">
+        <v>22</v>
+      </c>
+      <c r="I95" t="s">
+        <v>60</v>
+      </c>
+      <c r="J95" t="s">
+        <v>23</v>
+      </c>
+      <c r="K95" t="b">
+        <v>1</v>
+      </c>
+      <c r="L95" t="s">
+        <v>17</v>
+      </c>
+      <c r="M95" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96" t="s">
+        <v>136</v>
+      </c>
+      <c r="C96" t="s">
+        <v>143</v>
+      </c>
+      <c r="D96" t="s">
+        <v>212</v>
+      </c>
+      <c r="F96" t="s">
+        <v>41</v>
+      </c>
+      <c r="G96" t="s">
+        <v>21</v>
+      </c>
+      <c r="H96" t="s">
+        <v>22</v>
+      </c>
+      <c r="I96" t="s">
+        <v>60</v>
+      </c>
+      <c r="J96" t="s">
+        <v>23</v>
+      </c>
+      <c r="K96" t="b">
+        <v>1</v>
+      </c>
+      <c r="L96" t="s">
+        <v>17</v>
+      </c>
+      <c r="M96" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>32</v>
+      </c>
+      <c r="B97" t="s">
+        <v>136</v>
+      </c>
+      <c r="C97" t="s">
+        <v>160</v>
+      </c>
+      <c r="D97" t="s">
+        <v>161</v>
+      </c>
+      <c r="F97" t="s">
+        <v>41</v>
+      </c>
+      <c r="G97" t="s">
+        <v>21</v>
+      </c>
+      <c r="H97" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" t="s">
+        <v>60</v>
+      </c>
+      <c r="J97" t="s">
+        <v>23</v>
+      </c>
+      <c r="K97" t="b">
+        <v>1</v>
+      </c>
+      <c r="L97" t="s">
+        <v>17</v>
+      </c>
+      <c r="M97" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98" t="s">
+        <v>136</v>
+      </c>
+      <c r="C98" t="s">
+        <v>160</v>
+      </c>
+      <c r="D98" t="s">
+        <v>213</v>
+      </c>
+      <c r="F98" t="s">
+        <v>41</v>
+      </c>
+      <c r="G98" t="s">
+        <v>21</v>
+      </c>
+      <c r="H98" t="s">
+        <v>22</v>
+      </c>
+      <c r="I98" t="s">
+        <v>60</v>
+      </c>
+      <c r="J98" t="s">
+        <v>23</v>
+      </c>
+      <c r="K98" t="b">
+        <v>1</v>
+      </c>
+      <c r="L98" t="s">
+        <v>17</v>
+      </c>
+      <c r="M98" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>32</v>
+      </c>
+      <c r="B99" t="s">
+        <v>136</v>
+      </c>
+      <c r="C99" t="s">
+        <v>160</v>
+      </c>
+      <c r="D99" t="s">
+        <v>162</v>
+      </c>
+      <c r="F99" t="s">
+        <v>41</v>
+      </c>
+      <c r="G99" t="s">
+        <v>21</v>
+      </c>
+      <c r="H99" t="s">
+        <v>22</v>
+      </c>
+      <c r="I99" t="s">
+        <v>60</v>
+      </c>
+      <c r="J99" t="s">
+        <v>23</v>
+      </c>
+      <c r="K99" t="b">
+        <v>1</v>
+      </c>
+      <c r="L99" t="s">
+        <v>17</v>
+      </c>
+      <c r="M99" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100" t="s">
+        <v>136</v>
+      </c>
+      <c r="C100" t="s">
+        <v>160</v>
+      </c>
+      <c r="D100" t="s">
+        <v>163</v>
+      </c>
+      <c r="F100" t="s">
+        <v>41</v>
+      </c>
+      <c r="G100" t="s">
+        <v>21</v>
+      </c>
+      <c r="H100" t="s">
+        <v>22</v>
+      </c>
+      <c r="I100" t="s">
+        <v>60</v>
+      </c>
+      <c r="J100" t="s">
+        <v>23</v>
+      </c>
+      <c r="K100" t="b">
+        <v>1</v>
+      </c>
+      <c r="L100" t="s">
+        <v>17</v>
+      </c>
+      <c r="M100" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>32</v>
+      </c>
+      <c r="B101" t="s">
+        <v>136</v>
+      </c>
+      <c r="C101" t="s">
+        <v>160</v>
+      </c>
+      <c r="D101" t="s">
+        <v>164</v>
+      </c>
+      <c r="F101" t="s">
+        <v>41</v>
+      </c>
+      <c r="G101" t="s">
+        <v>21</v>
+      </c>
+      <c r="H101" t="s">
+        <v>22</v>
+      </c>
+      <c r="I101" t="s">
+        <v>60</v>
+      </c>
+      <c r="J101" t="s">
+        <v>23</v>
+      </c>
+      <c r="K101" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" t="s">
+        <v>17</v>
+      </c>
+      <c r="M101" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>32</v>
+      </c>
+      <c r="B102" t="s">
+        <v>136</v>
+      </c>
+      <c r="C102" t="s">
+        <v>160</v>
+      </c>
+      <c r="D102" t="s">
+        <v>165</v>
+      </c>
+      <c r="F102" t="s">
+        <v>41</v>
+      </c>
+      <c r="G102" t="s">
+        <v>21</v>
+      </c>
+      <c r="H102" t="s">
+        <v>22</v>
+      </c>
+      <c r="I102" t="s">
+        <v>60</v>
+      </c>
+      <c r="J102" t="s">
+        <v>23</v>
+      </c>
+      <c r="K102" t="b">
+        <v>1</v>
+      </c>
+      <c r="L102" t="s">
+        <v>17</v>
+      </c>
+      <c r="M102" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>32</v>
+      </c>
+      <c r="B103" t="s">
+        <v>136</v>
+      </c>
+      <c r="C103" t="s">
+        <v>160</v>
+      </c>
+      <c r="D103" t="s">
+        <v>166</v>
+      </c>
+      <c r="F103" t="s">
+        <v>41</v>
+      </c>
+      <c r="G103" t="s">
+        <v>21</v>
+      </c>
+      <c r="H103" t="s">
+        <v>22</v>
+      </c>
+      <c r="I103" t="s">
+        <v>60</v>
+      </c>
+      <c r="J103" t="s">
+        <v>23</v>
+      </c>
+      <c r="K103" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103" t="s">
+        <v>17</v>
+      </c>
+      <c r="M103" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>32</v>
+      </c>
+      <c r="B104" t="s">
+        <v>136</v>
+      </c>
+      <c r="C104" t="s">
+        <v>160</v>
+      </c>
+      <c r="D104" t="s">
+        <v>167</v>
+      </c>
+      <c r="F104" t="s">
+        <v>41</v>
+      </c>
+      <c r="G104" t="s">
+        <v>21</v>
+      </c>
+      <c r="H104" t="s">
+        <v>22</v>
+      </c>
+      <c r="I104" t="s">
+        <v>60</v>
+      </c>
+      <c r="J104" t="s">
+        <v>23</v>
+      </c>
+      <c r="K104" t="b">
+        <v>1</v>
+      </c>
+      <c r="L104" t="s">
+        <v>17</v>
+      </c>
+      <c r="M104" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>32</v>
+      </c>
+      <c r="B105" t="s">
+        <v>136</v>
+      </c>
+      <c r="C105" t="s">
+        <v>160</v>
+      </c>
+      <c r="D105" t="s">
+        <v>202</v>
+      </c>
+      <c r="F105" t="s">
+        <v>41</v>
+      </c>
+      <c r="G105" t="s">
+        <v>21</v>
+      </c>
+      <c r="H105" t="s">
+        <v>22</v>
+      </c>
+      <c r="I105" t="s">
+        <v>60</v>
+      </c>
+      <c r="J105" t="s">
+        <v>23</v>
+      </c>
+      <c r="K105" t="b">
+        <v>1</v>
+      </c>
+      <c r="L105" t="s">
+        <v>17</v>
+      </c>
+      <c r="M105" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>32</v>
+      </c>
+      <c r="B106" t="s">
+        <v>136</v>
+      </c>
+      <c r="C106" t="s">
+        <v>160</v>
+      </c>
+      <c r="D106" t="s">
+        <v>168</v>
+      </c>
+      <c r="F106" t="s">
+        <v>41</v>
+      </c>
+      <c r="G106" t="s">
+        <v>21</v>
+      </c>
+      <c r="H106" t="s">
+        <v>22</v>
+      </c>
+      <c r="I106" t="s">
+        <v>60</v>
+      </c>
+      <c r="J106" t="s">
+        <v>23</v>
+      </c>
+      <c r="K106" t="b">
+        <v>1</v>
+      </c>
+      <c r="L106" t="s">
+        <v>17</v>
+      </c>
+      <c r="M106" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>32</v>
+      </c>
+      <c r="B107" t="s">
+        <v>136</v>
+      </c>
+      <c r="C107" t="s">
+        <v>160</v>
+      </c>
+      <c r="D107" t="s">
+        <v>203</v>
+      </c>
+      <c r="F107" t="s">
+        <v>41</v>
+      </c>
+      <c r="G107" t="s">
+        <v>21</v>
+      </c>
+      <c r="H107" t="s">
+        <v>22</v>
+      </c>
+      <c r="I107" t="s">
+        <v>60</v>
+      </c>
+      <c r="J107" t="s">
+        <v>23</v>
+      </c>
+      <c r="K107" t="b">
+        <v>1</v>
+      </c>
+      <c r="L107" t="s">
+        <v>17</v>
+      </c>
+      <c r="M107" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>32</v>
+      </c>
+      <c r="B108" t="s">
+        <v>136</v>
+      </c>
+      <c r="C108" t="s">
+        <v>169</v>
+      </c>
+      <c r="D108" t="s">
+        <v>170</v>
+      </c>
+      <c r="F108" t="s">
+        <v>41</v>
+      </c>
+      <c r="G108" t="s">
+        <v>21</v>
+      </c>
+      <c r="H108" t="s">
+        <v>22</v>
+      </c>
+      <c r="I108" t="s">
+        <v>60</v>
+      </c>
+      <c r="J108" t="s">
+        <v>23</v>
+      </c>
+      <c r="K108" t="b">
+        <v>1</v>
+      </c>
+      <c r="L108" t="s">
+        <v>17</v>
+      </c>
+      <c r="M108" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>32</v>
+      </c>
+      <c r="B109" t="s">
+        <v>136</v>
+      </c>
+      <c r="C109" t="s">
+        <v>169</v>
+      </c>
+      <c r="D109" t="s">
+        <v>171</v>
+      </c>
+      <c r="F109" t="s">
+        <v>41</v>
+      </c>
+      <c r="G109" t="s">
+        <v>21</v>
+      </c>
+      <c r="H109" t="s">
+        <v>22</v>
+      </c>
+      <c r="I109" t="s">
+        <v>60</v>
+      </c>
+      <c r="J109" t="s">
+        <v>23</v>
+      </c>
+      <c r="K109" t="b">
+        <v>1</v>
+      </c>
+      <c r="L109" t="s">
+        <v>17</v>
+      </c>
+      <c r="M109" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>32</v>
+      </c>
+      <c r="B110" t="s">
+        <v>136</v>
+      </c>
+      <c r="C110" t="s">
+        <v>169</v>
+      </c>
+      <c r="D110" t="s">
+        <v>172</v>
+      </c>
+      <c r="F110" t="s">
+        <v>41</v>
+      </c>
+      <c r="G110" t="s">
+        <v>21</v>
+      </c>
+      <c r="H110" t="s">
+        <v>22</v>
+      </c>
+      <c r="I110" t="s">
+        <v>60</v>
+      </c>
+      <c r="J110" t="s">
+        <v>23</v>
+      </c>
+      <c r="K110" t="b">
+        <v>1</v>
+      </c>
+      <c r="L110" t="s">
+        <v>17</v>
+      </c>
+      <c r="M110" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>32</v>
+      </c>
+      <c r="B111" t="s">
+        <v>136</v>
+      </c>
+      <c r="C111" t="s">
+        <v>169</v>
+      </c>
+      <c r="D111" t="s">
+        <v>173</v>
+      </c>
+      <c r="F111" t="s">
+        <v>41</v>
+      </c>
+      <c r="G111" t="s">
+        <v>21</v>
+      </c>
+      <c r="H111" t="s">
+        <v>22</v>
+      </c>
+      <c r="I111" t="s">
+        <v>60</v>
+      </c>
+      <c r="J111" t="s">
+        <v>23</v>
+      </c>
+      <c r="K111" t="b">
+        <v>1</v>
+      </c>
+      <c r="L111" t="s">
+        <v>17</v>
+      </c>
+      <c r="M111" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>32</v>
+      </c>
+      <c r="B112" t="s">
+        <v>136</v>
+      </c>
+      <c r="C112" t="s">
+        <v>169</v>
+      </c>
+      <c r="D112" t="s">
+        <v>174</v>
+      </c>
+      <c r="F112" t="s">
+        <v>41</v>
+      </c>
+      <c r="G112" t="s">
+        <v>21</v>
+      </c>
+      <c r="H112" t="s">
+        <v>22</v>
+      </c>
+      <c r="I112" t="s">
+        <v>60</v>
+      </c>
+      <c r="J112" t="s">
+        <v>23</v>
+      </c>
+      <c r="K112" t="b">
+        <v>1</v>
+      </c>
+      <c r="L112" t="s">
+        <v>17</v>
+      </c>
+      <c r="M112" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>32</v>
+      </c>
+      <c r="B113" t="s">
+        <v>136</v>
+      </c>
+      <c r="C113" t="s">
+        <v>180</v>
+      </c>
+      <c r="D113" t="s">
+        <v>175</v>
+      </c>
+      <c r="F113" t="s">
+        <v>41</v>
+      </c>
+      <c r="G113" t="s">
+        <v>21</v>
+      </c>
+      <c r="H113" t="s">
+        <v>22</v>
+      </c>
+      <c r="I113" t="s">
+        <v>60</v>
+      </c>
+      <c r="J113" t="s">
+        <v>23</v>
+      </c>
+      <c r="K113" t="b">
+        <v>1</v>
+      </c>
+      <c r="L113" t="s">
+        <v>17</v>
+      </c>
+      <c r="M113" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>32</v>
+      </c>
+      <c r="B114" t="s">
+        <v>136</v>
+      </c>
+      <c r="C114" t="s">
+        <v>180</v>
+      </c>
+      <c r="D114" t="s">
+        <v>176</v>
+      </c>
+      <c r="F114" t="s">
+        <v>41</v>
+      </c>
+      <c r="G114" t="s">
+        <v>21</v>
+      </c>
+      <c r="H114" t="s">
+        <v>22</v>
+      </c>
+      <c r="I114" t="s">
+        <v>60</v>
+      </c>
+      <c r="J114" t="s">
+        <v>23</v>
+      </c>
+      <c r="K114" t="b">
+        <v>1</v>
+      </c>
+      <c r="L114" t="s">
+        <v>17</v>
+      </c>
+      <c r="M114" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>32</v>
+      </c>
+      <c r="B115" t="s">
+        <v>136</v>
+      </c>
+      <c r="C115" t="s">
+        <v>180</v>
+      </c>
+      <c r="D115" t="s">
+        <v>177</v>
+      </c>
+      <c r="F115" t="s">
+        <v>41</v>
+      </c>
+      <c r="G115" t="s">
+        <v>21</v>
+      </c>
+      <c r="H115" t="s">
+        <v>22</v>
+      </c>
+      <c r="I115" t="s">
+        <v>60</v>
+      </c>
+      <c r="J115" t="s">
+        <v>23</v>
+      </c>
+      <c r="K115" t="b">
+        <v>1</v>
+      </c>
+      <c r="L115" t="s">
+        <v>17</v>
+      </c>
+      <c r="M115" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>32</v>
+      </c>
+      <c r="B116" t="s">
+        <v>136</v>
+      </c>
+      <c r="C116" t="s">
+        <v>180</v>
+      </c>
+      <c r="D116" t="s">
+        <v>178</v>
+      </c>
+      <c r="F116" t="s">
+        <v>41</v>
+      </c>
+      <c r="G116" t="s">
+        <v>21</v>
+      </c>
+      <c r="H116" t="s">
+        <v>22</v>
+      </c>
+      <c r="I116" t="s">
+        <v>60</v>
+      </c>
+      <c r="J116" t="s">
+        <v>23</v>
+      </c>
+      <c r="K116" t="b">
+        <v>1</v>
+      </c>
+      <c r="L116" t="s">
+        <v>17</v>
+      </c>
+      <c r="M116" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>32</v>
+      </c>
+      <c r="B117" t="s">
+        <v>136</v>
+      </c>
+      <c r="C117" t="s">
+        <v>180</v>
+      </c>
+      <c r="D117" t="s">
+        <v>179</v>
+      </c>
+      <c r="F117" t="s">
+        <v>41</v>
+      </c>
+      <c r="G117" t="s">
+        <v>21</v>
+      </c>
+      <c r="H117" t="s">
+        <v>22</v>
+      </c>
+      <c r="I117" t="s">
+        <v>60</v>
+      </c>
+      <c r="J117" t="s">
+        <v>23</v>
+      </c>
+      <c r="K117" t="b">
+        <v>1</v>
+      </c>
+      <c r="L117" t="s">
+        <v>17</v>
+      </c>
+      <c r="M117" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>32</v>
+      </c>
+      <c r="B118" t="s">
+        <v>136</v>
+      </c>
+      <c r="C118" t="s">
+        <v>180</v>
+      </c>
+      <c r="D118" t="s">
+        <v>214</v>
+      </c>
+      <c r="F118" t="s">
+        <v>41</v>
+      </c>
+      <c r="G118" t="s">
+        <v>21</v>
+      </c>
+      <c r="H118" t="s">
+        <v>22</v>
+      </c>
+      <c r="I118" t="s">
+        <v>60</v>
+      </c>
+      <c r="J118" t="s">
+        <v>23</v>
+      </c>
+      <c r="K118" t="b">
+        <v>1</v>
+      </c>
+      <c r="L118" t="s">
+        <v>17</v>
+      </c>
+      <c r="M118" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>32</v>
+      </c>
+      <c r="B119" t="s">
+        <v>136</v>
+      </c>
+      <c r="C119" t="s">
+        <v>181</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F119" t="s">
+        <v>41</v>
+      </c>
+      <c r="G119" t="s">
+        <v>21</v>
+      </c>
+      <c r="H119" t="s">
+        <v>22</v>
+      </c>
+      <c r="I119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J119" t="s">
+        <v>23</v>
+      </c>
+      <c r="K119" t="b">
+        <v>1</v>
+      </c>
+      <c r="L119" t="s">
+        <v>17</v>
+      </c>
+      <c r="M119" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>32</v>
+      </c>
+      <c r="B120" t="s">
+        <v>136</v>
+      </c>
+      <c r="C120" t="s">
+        <v>181</v>
+      </c>
+      <c r="D120" t="s">
+        <v>205</v>
+      </c>
+      <c r="F120" t="s">
+        <v>41</v>
+      </c>
+      <c r="G120" t="s">
+        <v>21</v>
+      </c>
+      <c r="H120" t="s">
+        <v>22</v>
+      </c>
+      <c r="I120" t="s">
+        <v>60</v>
+      </c>
+      <c r="J120" t="s">
+        <v>23</v>
+      </c>
+      <c r="K120" t="b">
+        <v>1</v>
+      </c>
+      <c r="L120" t="s">
+        <v>17</v>
+      </c>
+      <c r="M120" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>32</v>
+      </c>
+      <c r="B121" t="s">
+        <v>136</v>
+      </c>
+      <c r="C121" t="s">
+        <v>181</v>
+      </c>
+      <c r="D121" t="s">
+        <v>182</v>
+      </c>
+      <c r="F121" t="s">
+        <v>41</v>
+      </c>
+      <c r="G121" t="s">
+        <v>21</v>
+      </c>
+      <c r="H121" t="s">
+        <v>22</v>
+      </c>
+      <c r="I121" t="s">
+        <v>60</v>
+      </c>
+      <c r="J121" t="s">
+        <v>23</v>
+      </c>
+      <c r="K121" t="b">
+        <v>1</v>
+      </c>
+      <c r="L121" t="s">
+        <v>17</v>
+      </c>
+      <c r="M121" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>32</v>
+      </c>
+      <c r="B122" t="s">
+        <v>136</v>
+      </c>
+      <c r="C122" t="s">
+        <v>181</v>
+      </c>
+      <c r="D122" t="s">
+        <v>183</v>
+      </c>
+      <c r="F122" t="s">
+        <v>41</v>
+      </c>
+      <c r="G122" t="s">
+        <v>21</v>
+      </c>
+      <c r="H122" t="s">
+        <v>22</v>
+      </c>
+      <c r="I122" t="s">
+        <v>60</v>
+      </c>
+      <c r="J122" t="s">
+        <v>23</v>
+      </c>
+      <c r="K122" t="b">
+        <v>1</v>
+      </c>
+      <c r="L122" t="s">
+        <v>17</v>
+      </c>
+      <c r="M122" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>32</v>
+      </c>
+      <c r="B123" t="s">
+        <v>136</v>
+      </c>
+      <c r="C123" t="s">
+        <v>181</v>
+      </c>
+      <c r="D123" t="s">
+        <v>206</v>
+      </c>
+      <c r="F123" t="s">
+        <v>41</v>
+      </c>
+      <c r="G123" t="s">
+        <v>21</v>
+      </c>
+      <c r="H123" t="s">
+        <v>22</v>
+      </c>
+      <c r="I123" t="s">
+        <v>60</v>
+      </c>
+      <c r="J123" t="s">
+        <v>23</v>
+      </c>
+      <c r="K123" t="b">
+        <v>1</v>
+      </c>
+      <c r="L123" t="s">
+        <v>17</v>
+      </c>
+      <c r="M123" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>32</v>
+      </c>
+      <c r="B124" t="s">
+        <v>136</v>
+      </c>
+      <c r="C124" t="s">
+        <v>181</v>
+      </c>
+      <c r="D124" t="s">
+        <v>184</v>
+      </c>
+      <c r="F124" t="s">
+        <v>41</v>
+      </c>
+      <c r="G124" t="s">
+        <v>21</v>
+      </c>
+      <c r="H124" t="s">
+        <v>22</v>
+      </c>
+      <c r="I124" t="s">
+        <v>60</v>
+      </c>
+      <c r="J124" t="s">
+        <v>23</v>
+      </c>
+      <c r="K124" t="b">
+        <v>1</v>
+      </c>
+      <c r="L124" t="s">
+        <v>17</v>
+      </c>
+      <c r="M124" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>32</v>
+      </c>
+      <c r="B125" t="s">
+        <v>185</v>
+      </c>
+      <c r="C125" t="s">
+        <v>186</v>
+      </c>
+      <c r="D125" t="s">
+        <v>187</v>
+      </c>
+      <c r="F125" t="s">
+        <v>41</v>
+      </c>
+      <c r="G125" t="s">
+        <v>21</v>
+      </c>
+      <c r="H125" t="s">
+        <v>22</v>
+      </c>
+      <c r="I125" t="s">
+        <v>60</v>
+      </c>
+      <c r="J125" t="s">
+        <v>23</v>
+      </c>
+      <c r="K125" t="b">
+        <v>1</v>
+      </c>
+      <c r="L125" t="s">
+        <v>17</v>
+      </c>
+      <c r="M125" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>32</v>
+      </c>
+      <c r="B126" t="s">
+        <v>185</v>
+      </c>
+      <c r="C126" t="s">
+        <v>186</v>
+      </c>
+      <c r="D126" t="s">
+        <v>188</v>
+      </c>
+      <c r="F126" t="s">
+        <v>41</v>
+      </c>
+      <c r="G126" t="s">
+        <v>21</v>
+      </c>
+      <c r="H126" t="s">
+        <v>22</v>
+      </c>
+      <c r="I126" t="s">
+        <v>60</v>
+      </c>
+      <c r="J126" t="s">
+        <v>23</v>
+      </c>
+      <c r="K126" t="b">
+        <v>1</v>
+      </c>
+      <c r="L126" t="s">
+        <v>17</v>
+      </c>
+      <c r="M126" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>32</v>
+      </c>
+      <c r="B127" t="s">
+        <v>185</v>
+      </c>
+      <c r="C127" t="s">
+        <v>189</v>
+      </c>
+      <c r="D127" t="s">
+        <v>190</v>
+      </c>
+      <c r="F127" t="s">
+        <v>41</v>
+      </c>
+      <c r="G127" t="s">
+        <v>21</v>
+      </c>
+      <c r="H127" t="s">
+        <v>22</v>
+      </c>
+      <c r="I127" t="s">
+        <v>60</v>
+      </c>
+      <c r="J127" t="s">
+        <v>23</v>
+      </c>
+      <c r="K127" t="b">
+        <v>1</v>
+      </c>
+      <c r="L127" t="s">
+        <v>17</v>
+      </c>
+      <c r="M127" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>32</v>
+      </c>
+      <c r="B128" t="s">
+        <v>185</v>
+      </c>
+      <c r="C128" t="s">
+        <v>189</v>
+      </c>
+      <c r="D128" t="s">
+        <v>191</v>
+      </c>
+      <c r="F128" t="s">
+        <v>41</v>
+      </c>
+      <c r="G128" t="s">
+        <v>21</v>
+      </c>
+      <c r="H128" t="s">
+        <v>22</v>
+      </c>
+      <c r="I128" t="s">
+        <v>60</v>
+      </c>
+      <c r="J128" t="s">
+        <v>23</v>
+      </c>
+      <c r="K128" t="b">
+        <v>1</v>
+      </c>
+      <c r="L128" t="s">
+        <v>17</v>
+      </c>
+      <c r="M128" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>32</v>
+      </c>
+      <c r="B129" t="s">
+        <v>185</v>
+      </c>
+      <c r="C129" t="s">
+        <v>189</v>
+      </c>
+      <c r="D129" t="s">
+        <v>192</v>
+      </c>
+      <c r="F129" t="s">
+        <v>41</v>
+      </c>
+      <c r="G129" t="s">
+        <v>21</v>
+      </c>
+      <c r="H129" t="s">
+        <v>22</v>
+      </c>
+      <c r="I129" t="s">
+        <v>60</v>
+      </c>
+      <c r="J129" t="s">
+        <v>23</v>
+      </c>
+      <c r="K129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L129" t="s">
+        <v>17</v>
+      </c>
+      <c r="M129" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>32</v>
+      </c>
+      <c r="B130" t="s">
+        <v>185</v>
+      </c>
+      <c r="C130" t="s">
+        <v>189</v>
+      </c>
+      <c r="D130" t="s">
+        <v>193</v>
+      </c>
+      <c r="F130" t="s">
+        <v>41</v>
+      </c>
+      <c r="G130" t="s">
+        <v>21</v>
+      </c>
+      <c r="H130" t="s">
+        <v>22</v>
+      </c>
+      <c r="I130" t="s">
+        <v>60</v>
+      </c>
+      <c r="J130" t="s">
+        <v>23</v>
+      </c>
+      <c r="K130" t="b">
+        <v>1</v>
+      </c>
+      <c r="L130" t="s">
+        <v>17</v>
+      </c>
+      <c r="M130" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>32</v>
+      </c>
+      <c r="B131" t="s">
+        <v>185</v>
+      </c>
+      <c r="C131" t="s">
+        <v>189</v>
+      </c>
+      <c r="D131" t="s">
+        <v>194</v>
+      </c>
+      <c r="F131" t="s">
+        <v>41</v>
+      </c>
+      <c r="G131" t="s">
+        <v>21</v>
+      </c>
+      <c r="H131" t="s">
+        <v>22</v>
+      </c>
+      <c r="I131" t="s">
+        <v>60</v>
+      </c>
+      <c r="J131" t="s">
+        <v>23</v>
+      </c>
+      <c r="K131" t="b">
+        <v>1</v>
+      </c>
+      <c r="L131" t="s">
+        <v>17</v>
+      </c>
+      <c r="M131" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>32</v>
+      </c>
+      <c r="B132" t="s">
+        <v>195</v>
+      </c>
+      <c r="C132" t="s">
+        <v>196</v>
+      </c>
+      <c r="D132" t="s">
+        <v>197</v>
+      </c>
+      <c r="E132" t="s">
+        <v>227</v>
+      </c>
+      <c r="F132" t="s">
+        <v>41</v>
+      </c>
+      <c r="G132" t="s">
+        <v>21</v>
+      </c>
+      <c r="H132" t="s">
+        <v>22</v>
+      </c>
+      <c r="I132" t="s">
+        <v>60</v>
+      </c>
+      <c r="J132" t="s">
+        <v>23</v>
+      </c>
+      <c r="K132" t="b">
+        <v>1</v>
+      </c>
+      <c r="L132" t="s">
+        <v>17</v>
+      </c>
+      <c r="M132" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>32</v>
+      </c>
+      <c r="B133" t="s">
+        <v>195</v>
+      </c>
+      <c r="C133" t="s">
+        <v>196</v>
+      </c>
+      <c r="D133" t="s">
+        <v>198</v>
+      </c>
+      <c r="E133" t="s">
+        <v>227</v>
+      </c>
+      <c r="F133" t="s">
+        <v>41</v>
+      </c>
+      <c r="G133" t="s">
+        <v>21</v>
+      </c>
+      <c r="H133" t="s">
+        <v>22</v>
+      </c>
+      <c r="I133" t="s">
+        <v>60</v>
+      </c>
+      <c r="J133" t="s">
+        <v>23</v>
+      </c>
+      <c r="K133" t="b">
+        <v>1</v>
+      </c>
+      <c r="L133" t="s">
+        <v>17</v>
+      </c>
+      <c r="M133" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>32</v>
+      </c>
+      <c r="B134" t="s">
+        <v>195</v>
+      </c>
+      <c r="C134" t="s">
+        <v>196</v>
+      </c>
+      <c r="D134" t="s">
+        <v>199</v>
+      </c>
+      <c r="E134" t="s">
+        <v>227</v>
+      </c>
+      <c r="F134" t="s">
+        <v>41</v>
+      </c>
+      <c r="G134" t="s">
+        <v>21</v>
+      </c>
+      <c r="H134" t="s">
+        <v>22</v>
+      </c>
+      <c r="I134" t="s">
+        <v>60</v>
+      </c>
+      <c r="J134" t="s">
+        <v>23</v>
+      </c>
+      <c r="K134" t="b">
+        <v>1</v>
+      </c>
+      <c r="L134" t="s">
+        <v>17</v>
+      </c>
+      <c r="M134" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>32</v>
+      </c>
+      <c r="B135" t="s">
+        <v>195</v>
+      </c>
+      <c r="C135" t="s">
+        <v>196</v>
+      </c>
+      <c r="D135" t="s">
+        <v>201</v>
+      </c>
+      <c r="E135" t="s">
+        <v>227</v>
+      </c>
+      <c r="F135" t="s">
+        <v>41</v>
+      </c>
+      <c r="G135" t="s">
+        <v>21</v>
+      </c>
+      <c r="H135" t="s">
+        <v>22</v>
+      </c>
+      <c r="I135" t="s">
+        <v>60</v>
+      </c>
+      <c r="J135" t="s">
+        <v>23</v>
+      </c>
+      <c r="K135" t="b">
+        <v>1</v>
+      </c>
+      <c r="L135" t="s">
+        <v>17</v>
+      </c>
+      <c r="M135" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>32</v>
+      </c>
+      <c r="B136" t="s">
+        <v>195</v>
+      </c>
+      <c r="C136" t="s">
+        <v>196</v>
+      </c>
+      <c r="D136" t="s">
+        <v>200</v>
+      </c>
+      <c r="E136" t="s">
+        <v>227</v>
+      </c>
+      <c r="F136" t="s">
+        <v>41</v>
+      </c>
+      <c r="G136" t="s">
+        <v>21</v>
+      </c>
+      <c r="H136" t="s">
+        <v>22</v>
+      </c>
+      <c r="I136" t="s">
+        <v>60</v>
+      </c>
+      <c r="J136" t="s">
+        <v>23</v>
+      </c>
+      <c r="K136" t="b">
+        <v>1</v>
+      </c>
+      <c r="L136" t="s">
+        <v>17</v>
+      </c>
+      <c r="M136" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>32</v>
+      </c>
+      <c r="B137" t="s">
+        <v>195</v>
+      </c>
+      <c r="C137" t="s">
+        <v>196</v>
+      </c>
+      <c r="D137" t="s">
+        <v>215</v>
+      </c>
+      <c r="E137" t="s">
+        <v>227</v>
+      </c>
+      <c r="F137" t="s">
+        <v>41</v>
+      </c>
+      <c r="G137" t="s">
+        <v>21</v>
+      </c>
+      <c r="H137" t="s">
+        <v>22</v>
+      </c>
+      <c r="I137" t="s">
+        <v>60</v>
+      </c>
+      <c r="J137" t="s">
+        <v>23</v>
+      </c>
+      <c r="K137" t="b">
+        <v>1</v>
+      </c>
+      <c r="L137" t="s">
+        <v>17</v>
+      </c>
+      <c r="M137" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>32</v>
+      </c>
+      <c r="B138" t="s">
+        <v>195</v>
+      </c>
+      <c r="C138" t="s">
+        <v>196</v>
+      </c>
+      <c r="D138" t="s">
+        <v>216</v>
+      </c>
+      <c r="E138" t="s">
+        <v>227</v>
+      </c>
+      <c r="F138" t="s">
+        <v>41</v>
+      </c>
+      <c r="G138" t="s">
+        <v>21</v>
+      </c>
+      <c r="H138" t="s">
+        <v>22</v>
+      </c>
+      <c r="I138" t="s">
+        <v>60</v>
+      </c>
+      <c r="J138" t="s">
+        <v>23</v>
+      </c>
+      <c r="K138" t="b">
+        <v>1</v>
+      </c>
+      <c r="L138" t="s">
+        <v>17</v>
+      </c>
+      <c r="M138" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>32</v>
+      </c>
+      <c r="B139" t="s">
+        <v>217</v>
+      </c>
+      <c r="C139" t="s">
+        <v>218</v>
+      </c>
+      <c r="D139" t="s">
+        <v>219</v>
+      </c>
+      <c r="E139" t="s">
+        <v>226</v>
+      </c>
+      <c r="F139" t="s">
+        <v>41</v>
+      </c>
+      <c r="G139" t="s">
+        <v>21</v>
+      </c>
+      <c r="H139" t="s">
+        <v>22</v>
+      </c>
+      <c r="I139" t="s">
+        <v>60</v>
+      </c>
+      <c r="J139" t="s">
+        <v>23</v>
+      </c>
+      <c r="K139" t="b">
+        <v>1</v>
+      </c>
+      <c r="L139" t="s">
+        <v>17</v>
+      </c>
+      <c r="M139" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>32</v>
+      </c>
+      <c r="B140" t="s">
+        <v>217</v>
+      </c>
+      <c r="C140" t="s">
+        <v>218</v>
+      </c>
+      <c r="D140" t="s">
+        <v>224</v>
+      </c>
+      <c r="E140" t="s">
+        <v>226</v>
+      </c>
+      <c r="F140" t="s">
+        <v>41</v>
+      </c>
+      <c r="G140" t="s">
+        <v>21</v>
+      </c>
+      <c r="H140" t="s">
+        <v>22</v>
+      </c>
+      <c r="I140" t="s">
+        <v>60</v>
+      </c>
+      <c r="J140" t="s">
+        <v>23</v>
+      </c>
+      <c r="K140" t="b">
+        <v>1</v>
+      </c>
+      <c r="L140" t="s">
+        <v>17</v>
+      </c>
+      <c r="M140" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>32</v>
+      </c>
+      <c r="B141" t="s">
+        <v>217</v>
+      </c>
+      <c r="C141" t="s">
+        <v>218</v>
+      </c>
+      <c r="D141" t="s">
+        <v>220</v>
+      </c>
+      <c r="E141" t="s">
+        <v>226</v>
+      </c>
+      <c r="F141" t="s">
+        <v>41</v>
+      </c>
+      <c r="G141" t="s">
+        <v>21</v>
+      </c>
+      <c r="H141" t="s">
+        <v>22</v>
+      </c>
+      <c r="I141" t="s">
+        <v>60</v>
+      </c>
+      <c r="J141" t="s">
+        <v>23</v>
+      </c>
+      <c r="K141" t="b">
+        <v>1</v>
+      </c>
+      <c r="L141" t="s">
+        <v>17</v>
+      </c>
+      <c r="M141" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>32</v>
+      </c>
+      <c r="B142" t="s">
+        <v>217</v>
+      </c>
+      <c r="C142" t="s">
+        <v>218</v>
+      </c>
+      <c r="D142" t="s">
+        <v>221</v>
+      </c>
+      <c r="E142" t="s">
+        <v>226</v>
+      </c>
+      <c r="F142" t="s">
+        <v>41</v>
+      </c>
+      <c r="G142" t="s">
+        <v>21</v>
+      </c>
+      <c r="H142" t="s">
+        <v>22</v>
+      </c>
+      <c r="I142" t="s">
+        <v>60</v>
+      </c>
+      <c r="J142" t="s">
+        <v>23</v>
+      </c>
+      <c r="K142" t="b">
+        <v>1</v>
+      </c>
+      <c r="L142" t="s">
+        <v>17</v>
+      </c>
+      <c r="M142" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>32</v>
+      </c>
+      <c r="B143" t="s">
+        <v>217</v>
+      </c>
+      <c r="C143" t="s">
+        <v>218</v>
+      </c>
+      <c r="D143" t="s">
+        <v>222</v>
+      </c>
+      <c r="E143" t="s">
+        <v>226</v>
+      </c>
+      <c r="F143" t="s">
+        <v>41</v>
+      </c>
+      <c r="G143" t="s">
+        <v>21</v>
+      </c>
+      <c r="H143" t="s">
+        <v>22</v>
+      </c>
+      <c r="I143" t="s">
+        <v>60</v>
+      </c>
+      <c r="J143" t="s">
+        <v>23</v>
+      </c>
+      <c r="K143" t="b">
+        <v>1</v>
+      </c>
+      <c r="L143" t="s">
+        <v>17</v>
+      </c>
+      <c r="M143" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>32</v>
+      </c>
+      <c r="B144" t="s">
+        <v>217</v>
+      </c>
+      <c r="C144" t="s">
+        <v>218</v>
+      </c>
+      <c r="D144" t="s">
+        <v>223</v>
+      </c>
+      <c r="E144" t="s">
+        <v>226</v>
+      </c>
+      <c r="F144" t="s">
+        <v>41</v>
+      </c>
+      <c r="G144" t="s">
+        <v>21</v>
+      </c>
+      <c r="H144" t="s">
+        <v>22</v>
+      </c>
+      <c r="I144" t="s">
+        <v>60</v>
+      </c>
+      <c r="J144" t="s">
+        <v>23</v>
+      </c>
+      <c r="K144" t="b">
+        <v>1</v>
+      </c>
+      <c r="L144" t="s">
+        <v>17</v>
+      </c>
+      <c r="M144" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>32</v>
+      </c>
+      <c r="B145" t="s">
+        <v>217</v>
+      </c>
+      <c r="C145" t="s">
+        <v>218</v>
+      </c>
+      <c r="D145" t="s">
+        <v>225</v>
+      </c>
+      <c r="E145" t="s">
+        <v>226</v>
+      </c>
+      <c r="F145" t="s">
+        <v>41</v>
+      </c>
+      <c r="G145" t="s">
+        <v>21</v>
+      </c>
+      <c r="H145" t="s">
+        <v>22</v>
+      </c>
+      <c r="I145" t="s">
+        <v>60</v>
+      </c>
+      <c r="J145" t="s">
+        <v>23</v>
+      </c>
+      <c r="K145" t="b">
+        <v>1</v>
+      </c>
+      <c r="L145" t="s">
+        <v>17</v>
+      </c>
+      <c r="M145" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>32</v>
+      </c>
+      <c r="B146" t="s">
+        <v>217</v>
+      </c>
+      <c r="C146" t="s">
+        <v>228</v>
+      </c>
+      <c r="D146" t="s">
+        <v>229</v>
+      </c>
+      <c r="E146" t="s">
+        <v>234</v>
+      </c>
+      <c r="F146" t="s">
+        <v>41</v>
+      </c>
+      <c r="G146" t="s">
+        <v>21</v>
+      </c>
+      <c r="H146" t="s">
+        <v>22</v>
+      </c>
+      <c r="I146" t="s">
+        <v>60</v>
+      </c>
+      <c r="J146" t="s">
+        <v>23</v>
+      </c>
+      <c r="K146" t="b">
+        <v>1</v>
+      </c>
+      <c r="L146" t="s">
+        <v>17</v>
+      </c>
+      <c r="M146" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>32</v>
+      </c>
+      <c r="B147" t="s">
+        <v>217</v>
+      </c>
+      <c r="C147" t="s">
+        <v>228</v>
+      </c>
+      <c r="D147" t="s">
+        <v>230</v>
+      </c>
+      <c r="E147" t="s">
+        <v>234</v>
+      </c>
+      <c r="F147" t="s">
+        <v>41</v>
+      </c>
+      <c r="G147" t="s">
+        <v>21</v>
+      </c>
+      <c r="H147" t="s">
+        <v>22</v>
+      </c>
+      <c r="I147" t="s">
+        <v>60</v>
+      </c>
+      <c r="J147" t="s">
+        <v>23</v>
+      </c>
+      <c r="K147" t="b">
+        <v>1</v>
+      </c>
+      <c r="L147" t="s">
+        <v>17</v>
+      </c>
+      <c r="M147" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>32</v>
+      </c>
+      <c r="B148" t="s">
+        <v>217</v>
+      </c>
+      <c r="C148" t="s">
+        <v>228</v>
+      </c>
+      <c r="D148" t="s">
+        <v>231</v>
+      </c>
+      <c r="E148" t="s">
+        <v>234</v>
+      </c>
+      <c r="F148" t="s">
+        <v>41</v>
+      </c>
+      <c r="G148" t="s">
+        <v>21</v>
+      </c>
+      <c r="H148" t="s">
+        <v>22</v>
+      </c>
+      <c r="I148" t="s">
+        <v>60</v>
+      </c>
+      <c r="J148" t="s">
+        <v>23</v>
+      </c>
+      <c r="K148" t="b">
+        <v>1</v>
+      </c>
+      <c r="L148" t="s">
+        <v>17</v>
+      </c>
+      <c r="M148" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>32</v>
+      </c>
+      <c r="B149" t="s">
+        <v>217</v>
+      </c>
+      <c r="C149" t="s">
+        <v>228</v>
+      </c>
+      <c r="D149" t="s">
+        <v>232</v>
+      </c>
+      <c r="E149" t="s">
+        <v>234</v>
+      </c>
+      <c r="F149" t="s">
+        <v>41</v>
+      </c>
+      <c r="G149" t="s">
+        <v>21</v>
+      </c>
+      <c r="H149" t="s">
+        <v>22</v>
+      </c>
+      <c r="I149" t="s">
+        <v>60</v>
+      </c>
+      <c r="J149" t="s">
+        <v>23</v>
+      </c>
+      <c r="K149" t="b">
+        <v>1</v>
+      </c>
+      <c r="L149" t="s">
+        <v>17</v>
+      </c>
+      <c r="M149" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>32</v>
+      </c>
+      <c r="B150" t="s">
+        <v>217</v>
+      </c>
+      <c r="C150" t="s">
+        <v>228</v>
+      </c>
+      <c r="D150" t="s">
+        <v>233</v>
+      </c>
+      <c r="E150" t="s">
+        <v>234</v>
+      </c>
+      <c r="F150" t="s">
+        <v>41</v>
+      </c>
+      <c r="G150" t="s">
+        <v>21</v>
+      </c>
+      <c r="H150" t="s">
+        <v>22</v>
+      </c>
+      <c r="I150" t="s">
+        <v>60</v>
+      </c>
+      <c r="J150" t="s">
+        <v>23</v>
+      </c>
+      <c r="K150" t="b">
+        <v>1</v>
+      </c>
+      <c r="L150" t="s">
+        <v>17</v>
+      </c>
+      <c r="M150" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>32</v>
+      </c>
+      <c r="B151" t="s">
+        <v>217</v>
+      </c>
+      <c r="C151" t="s">
+        <v>228</v>
+      </c>
+      <c r="D151" t="s">
+        <v>239</v>
+      </c>
+      <c r="E151" t="s">
+        <v>234</v>
+      </c>
+      <c r="F151" t="s">
+        <v>41</v>
+      </c>
+      <c r="G151" t="s">
+        <v>21</v>
+      </c>
+      <c r="H151" t="s">
+        <v>22</v>
+      </c>
+      <c r="I151" t="s">
+        <v>60</v>
+      </c>
+      <c r="J151" t="s">
+        <v>23</v>
+      </c>
+      <c r="K151" t="b">
+        <v>1</v>
+      </c>
+      <c r="L151" t="s">
+        <v>17</v>
+      </c>
+      <c r="M151" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>32</v>
+      </c>
+      <c r="B152" t="s">
+        <v>217</v>
+      </c>
+      <c r="C152" t="s">
+        <v>228</v>
+      </c>
+      <c r="D152" t="s">
+        <v>240</v>
+      </c>
+      <c r="E152" t="s">
+        <v>234</v>
+      </c>
+      <c r="F152" t="s">
+        <v>41</v>
+      </c>
+      <c r="G152" t="s">
+        <v>21</v>
+      </c>
+      <c r="H152" t="s">
+        <v>22</v>
+      </c>
+      <c r="I152" t="s">
+        <v>60</v>
+      </c>
+      <c r="J152" t="s">
+        <v>23</v>
+      </c>
+      <c r="K152" t="b">
+        <v>1</v>
+      </c>
+      <c r="L152" t="s">
+        <v>17</v>
+      </c>
+      <c r="M152" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>32</v>
+      </c>
+      <c r="B153" t="s">
+        <v>217</v>
+      </c>
+      <c r="C153" t="s">
+        <v>228</v>
+      </c>
+      <c r="D153" t="s">
+        <v>235</v>
+      </c>
+      <c r="E153" t="s">
+        <v>234</v>
+      </c>
+      <c r="F153" t="s">
+        <v>41</v>
+      </c>
+      <c r="G153" t="s">
+        <v>21</v>
+      </c>
+      <c r="H153" t="s">
+        <v>22</v>
+      </c>
+      <c r="I153" t="s">
+        <v>60</v>
+      </c>
+      <c r="J153" t="s">
+        <v>23</v>
+      </c>
+      <c r="K153" t="b">
+        <v>1</v>
+      </c>
+      <c r="L153" t="s">
+        <v>17</v>
+      </c>
+      <c r="M153" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>32</v>
+      </c>
+      <c r="B154" t="s">
+        <v>217</v>
+      </c>
+      <c r="C154" t="s">
+        <v>228</v>
+      </c>
+      <c r="D154" t="s">
+        <v>241</v>
+      </c>
+      <c r="E154" t="s">
+        <v>234</v>
+      </c>
+      <c r="F154" t="s">
+        <v>41</v>
+      </c>
+      <c r="G154" t="s">
+        <v>21</v>
+      </c>
+      <c r="H154" t="s">
+        <v>22</v>
+      </c>
+      <c r="I154" t="s">
+        <v>60</v>
+      </c>
+      <c r="J154" t="s">
+        <v>23</v>
+      </c>
+      <c r="K154" t="b">
+        <v>1</v>
+      </c>
+      <c r="L154" t="s">
+        <v>17</v>
+      </c>
+      <c r="M154" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>32</v>
+      </c>
+      <c r="B155" t="s">
+        <v>217</v>
+      </c>
+      <c r="C155" t="s">
+        <v>228</v>
+      </c>
+      <c r="D155" t="s">
+        <v>242</v>
+      </c>
+      <c r="E155" t="s">
+        <v>234</v>
+      </c>
+      <c r="F155" t="s">
+        <v>41</v>
+      </c>
+      <c r="G155" t="s">
+        <v>21</v>
+      </c>
+      <c r="H155" t="s">
+        <v>22</v>
+      </c>
+      <c r="I155" t="s">
+        <v>60</v>
+      </c>
+      <c r="J155" t="s">
+        <v>23</v>
+      </c>
+      <c r="K155" t="b">
+        <v>1</v>
+      </c>
+      <c r="L155" t="s">
+        <v>17</v>
+      </c>
+      <c r="M155" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>32</v>
+      </c>
+      <c r="B156" t="s">
+        <v>217</v>
+      </c>
+      <c r="C156" t="s">
+        <v>228</v>
+      </c>
+      <c r="D156" t="s">
+        <v>243</v>
+      </c>
+      <c r="E156" t="s">
+        <v>234</v>
+      </c>
+      <c r="F156" t="s">
+        <v>41</v>
+      </c>
+      <c r="G156" t="s">
+        <v>21</v>
+      </c>
+      <c r="H156" t="s">
+        <v>22</v>
+      </c>
+      <c r="I156" t="s">
+        <v>60</v>
+      </c>
+      <c r="J156" t="s">
+        <v>23</v>
+      </c>
+      <c r="K156" t="b">
+        <v>1</v>
+      </c>
+      <c r="L156" t="s">
+        <v>17</v>
+      </c>
+      <c r="M156" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>32</v>
+      </c>
+      <c r="B157" t="s">
+        <v>217</v>
+      </c>
+      <c r="C157" t="s">
+        <v>228</v>
+      </c>
+      <c r="D157" t="s">
+        <v>236</v>
+      </c>
+      <c r="E157" t="s">
+        <v>234</v>
+      </c>
+      <c r="F157" t="s">
+        <v>41</v>
+      </c>
+      <c r="G157" t="s">
+        <v>21</v>
+      </c>
+      <c r="H157" t="s">
+        <v>22</v>
+      </c>
+      <c r="I157" t="s">
+        <v>60</v>
+      </c>
+      <c r="J157" t="s">
+        <v>23</v>
+      </c>
+      <c r="K157" t="b">
+        <v>1</v>
+      </c>
+      <c r="L157" t="s">
+        <v>17</v>
+      </c>
+      <c r="M157" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>32</v>
+      </c>
+      <c r="B158" t="s">
+        <v>217</v>
+      </c>
+      <c r="C158" t="s">
+        <v>228</v>
+      </c>
+      <c r="D158" t="s">
+        <v>237</v>
+      </c>
+      <c r="E158" t="s">
+        <v>234</v>
+      </c>
+      <c r="F158" t="s">
+        <v>41</v>
+      </c>
+      <c r="G158" t="s">
+        <v>21</v>
+      </c>
+      <c r="H158" t="s">
+        <v>22</v>
+      </c>
+      <c r="I158" t="s">
+        <v>60</v>
+      </c>
+      <c r="J158" t="s">
+        <v>23</v>
+      </c>
+      <c r="K158" t="b">
+        <v>1</v>
+      </c>
+      <c r="L158" t="s">
+        <v>17</v>
+      </c>
+      <c r="M158" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>32</v>
+      </c>
+      <c r="B159" t="s">
+        <v>217</v>
+      </c>
+      <c r="C159" t="s">
+        <v>228</v>
+      </c>
+      <c r="D159" t="s">
+        <v>244</v>
+      </c>
+      <c r="E159" t="s">
+        <v>234</v>
+      </c>
+      <c r="F159" t="s">
+        <v>41</v>
+      </c>
+      <c r="G159" t="s">
+        <v>21</v>
+      </c>
+      <c r="H159" t="s">
+        <v>22</v>
+      </c>
+      <c r="I159" t="s">
+        <v>60</v>
+      </c>
+      <c r="J159" t="s">
+        <v>23</v>
+      </c>
+      <c r="K159" t="b">
+        <v>1</v>
+      </c>
+      <c r="L159" t="s">
+        <v>17</v>
+      </c>
+      <c r="M159" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>32</v>
+      </c>
+      <c r="B160" t="s">
+        <v>217</v>
+      </c>
+      <c r="C160" t="s">
+        <v>228</v>
+      </c>
+      <c r="D160" t="s">
+        <v>238</v>
+      </c>
+      <c r="E160" t="s">
+        <v>234</v>
+      </c>
+      <c r="F160" t="s">
+        <v>41</v>
+      </c>
+      <c r="G160" t="s">
+        <v>21</v>
+      </c>
+      <c r="H160" t="s">
+        <v>22</v>
+      </c>
+      <c r="I160" t="s">
+        <v>60</v>
+      </c>
+      <c r="J160" t="s">
+        <v>23</v>
+      </c>
+      <c r="K160" t="b">
+        <v>1</v>
+      </c>
+      <c r="L160" t="s">
+        <v>17</v>
+      </c>
+      <c r="M160" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>32</v>
+      </c>
+      <c r="B161" t="s">
+        <v>217</v>
+      </c>
+      <c r="C161" t="s">
+        <v>228</v>
+      </c>
+      <c r="D161" t="s">
+        <v>245</v>
+      </c>
+      <c r="E161" t="s">
+        <v>234</v>
+      </c>
+      <c r="F161" t="s">
+        <v>41</v>
+      </c>
+      <c r="G161" t="s">
+        <v>21</v>
+      </c>
+      <c r="H161" t="s">
+        <v>22</v>
+      </c>
+      <c r="I161" t="s">
+        <v>60</v>
+      </c>
+      <c r="J161" t="s">
+        <v>23</v>
+      </c>
+      <c r="K161" t="b">
+        <v>1</v>
+      </c>
+      <c r="L161" t="s">
+        <v>17</v>
+      </c>
+      <c r="M161" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>32</v>
+      </c>
+      <c r="B162" t="s">
+        <v>217</v>
+      </c>
+      <c r="C162" t="s">
+        <v>228</v>
+      </c>
+      <c r="D162" t="s">
+        <v>246</v>
+      </c>
+      <c r="E162" t="s">
+        <v>234</v>
+      </c>
+      <c r="F162" t="s">
+        <v>41</v>
+      </c>
+      <c r="G162" t="s">
+        <v>21</v>
+      </c>
+      <c r="H162" t="s">
+        <v>22</v>
+      </c>
+      <c r="I162" t="s">
+        <v>60</v>
+      </c>
+      <c r="J162" t="s">
+        <v>23</v>
+      </c>
+      <c r="K162" t="b">
+        <v>1</v>
+      </c>
+      <c r="L162" t="s">
+        <v>17</v>
+      </c>
+      <c r="M162" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>32</v>
+      </c>
+      <c r="B163" t="s">
+        <v>217</v>
+      </c>
+      <c r="C163" t="s">
+        <v>228</v>
+      </c>
+      <c r="D163" t="s">
+        <v>247</v>
+      </c>
+      <c r="E163" t="s">
+        <v>234</v>
+      </c>
+      <c r="F163" t="s">
+        <v>41</v>
+      </c>
+      <c r="G163" t="s">
+        <v>21</v>
+      </c>
+      <c r="H163" t="s">
+        <v>22</v>
+      </c>
+      <c r="I163" t="s">
+        <v>60</v>
+      </c>
+      <c r="J163" t="s">
+        <v>23</v>
+      </c>
+      <c r="K163" t="b">
+        <v>1</v>
+      </c>
+      <c r="L163" t="s">
+        <v>17</v>
+      </c>
+      <c r="M163" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>32</v>
+      </c>
+      <c r="B164" t="s">
+        <v>217</v>
+      </c>
+      <c r="C164" t="s">
+        <v>228</v>
+      </c>
+      <c r="D164" t="s">
+        <v>248</v>
+      </c>
+      <c r="E164" t="s">
+        <v>234</v>
+      </c>
+      <c r="F164" t="s">
+        <v>41</v>
+      </c>
+      <c r="G164" t="s">
+        <v>21</v>
+      </c>
+      <c r="H164" t="s">
+        <v>22</v>
+      </c>
+      <c r="I164" t="s">
+        <v>60</v>
+      </c>
+      <c r="J164" t="s">
+        <v>23</v>
+      </c>
+      <c r="K164" t="b">
+        <v>1</v>
+      </c>
+      <c r="L164" t="s">
+        <v>17</v>
+      </c>
+      <c r="M164" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>32</v>
+      </c>
+      <c r="B165" t="s">
+        <v>217</v>
+      </c>
+      <c r="C165" t="s">
+        <v>228</v>
+      </c>
+      <c r="D165" t="s">
+        <v>249</v>
+      </c>
+      <c r="E165" t="s">
+        <v>234</v>
+      </c>
+      <c r="F165" t="s">
+        <v>41</v>
+      </c>
+      <c r="G165" t="s">
+        <v>21</v>
+      </c>
+      <c r="H165" t="s">
+        <v>22</v>
+      </c>
+      <c r="I165" t="s">
+        <v>60</v>
+      </c>
+      <c r="J165" t="s">
+        <v>23</v>
+      </c>
+      <c r="K165" t="b">
+        <v>1</v>
+      </c>
+      <c r="L165" t="s">
+        <v>17</v>
+      </c>
+      <c r="M165" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>32</v>
+      </c>
+      <c r="B166" t="s">
+        <v>217</v>
+      </c>
+      <c r="C166" t="s">
+        <v>228</v>
+      </c>
+      <c r="D166" t="s">
+        <v>250</v>
+      </c>
+      <c r="E166" t="s">
+        <v>234</v>
+      </c>
+      <c r="F166" t="s">
+        <v>41</v>
+      </c>
+      <c r="G166" t="s">
+        <v>21</v>
+      </c>
+      <c r="H166" t="s">
+        <v>22</v>
+      </c>
+      <c r="I166" t="s">
+        <v>60</v>
+      </c>
+      <c r="J166" t="s">
+        <v>23</v>
+      </c>
+      <c r="K166" t="b">
+        <v>1</v>
+      </c>
+      <c r="L166" t="s">
+        <v>17</v>
+      </c>
+      <c r="M166" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>32</v>
+      </c>
+      <c r="B167" t="s">
+        <v>217</v>
+      </c>
+      <c r="C167" t="s">
+        <v>228</v>
+      </c>
+      <c r="D167" t="s">
+        <v>251</v>
+      </c>
+      <c r="E167" t="s">
+        <v>234</v>
+      </c>
+      <c r="F167" t="s">
+        <v>41</v>
+      </c>
+      <c r="G167" t="s">
+        <v>21</v>
+      </c>
+      <c r="H167" t="s">
+        <v>22</v>
+      </c>
+      <c r="I167" t="s">
+        <v>60</v>
+      </c>
+      <c r="J167" t="s">
+        <v>23</v>
+      </c>
+      <c r="K167" t="b">
+        <v>1</v>
+      </c>
+      <c r="L167" t="s">
+        <v>17</v>
+      </c>
+      <c r="M167" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>32</v>
+      </c>
+      <c r="B168" t="s">
+        <v>217</v>
+      </c>
+      <c r="C168" t="s">
+        <v>228</v>
+      </c>
+      <c r="D168" t="s">
+        <v>252</v>
+      </c>
+      <c r="E168" t="s">
+        <v>234</v>
+      </c>
+      <c r="F168" t="s">
+        <v>41</v>
+      </c>
+      <c r="G168" t="s">
+        <v>21</v>
+      </c>
+      <c r="H168" t="s">
+        <v>22</v>
+      </c>
+      <c r="I168" t="s">
+        <v>60</v>
+      </c>
+      <c r="J168" t="s">
+        <v>23</v>
+      </c>
+      <c r="K168" t="b">
+        <v>1</v>
+      </c>
+      <c r="L168" t="s">
+        <v>17</v>
+      </c>
+      <c r="M168" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>32</v>
+      </c>
+      <c r="B169" t="s">
+        <v>217</v>
+      </c>
+      <c r="C169" t="s">
+        <v>228</v>
+      </c>
+      <c r="D169" t="s">
+        <v>253</v>
+      </c>
+      <c r="E169" t="s">
+        <v>234</v>
+      </c>
+      <c r="F169" t="s">
+        <v>41</v>
+      </c>
+      <c r="G169" t="s">
+        <v>21</v>
+      </c>
+      <c r="H169" t="s">
+        <v>22</v>
+      </c>
+      <c r="I169" t="s">
+        <v>60</v>
+      </c>
+      <c r="J169" t="s">
+        <v>23</v>
+      </c>
+      <c r="K169" t="b">
+        <v>1</v>
+      </c>
+      <c r="L169" t="s">
+        <v>17</v>
+      </c>
+      <c r="M169" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>32</v>
+      </c>
+      <c r="B170" t="s">
+        <v>217</v>
+      </c>
+      <c r="C170" t="s">
+        <v>228</v>
+      </c>
+      <c r="D170" t="s">
+        <v>254</v>
+      </c>
+      <c r="E170" t="s">
+        <v>234</v>
+      </c>
+      <c r="F170" t="s">
+        <v>41</v>
+      </c>
+      <c r="G170" t="s">
+        <v>21</v>
+      </c>
+      <c r="H170" t="s">
+        <v>22</v>
+      </c>
+      <c r="I170" t="s">
+        <v>60</v>
+      </c>
+      <c r="J170" t="s">
+        <v>23</v>
+      </c>
+      <c r="K170" t="b">
+        <v>1</v>
+      </c>
+      <c r="L170" t="s">
+        <v>17</v>
+      </c>
+      <c r="M170" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>32</v>
+      </c>
+      <c r="B171" t="s">
+        <v>217</v>
+      </c>
+      <c r="C171" t="s">
+        <v>228</v>
+      </c>
+      <c r="D171" t="s">
+        <v>255</v>
+      </c>
+      <c r="E171" t="s">
+        <v>234</v>
+      </c>
+      <c r="F171" t="s">
+        <v>41</v>
+      </c>
+      <c r="G171" t="s">
+        <v>21</v>
+      </c>
+      <c r="H171" t="s">
+        <v>22</v>
+      </c>
+      <c r="I171" t="s">
+        <v>60</v>
+      </c>
+      <c r="J171" t="s">
+        <v>23</v>
+      </c>
+      <c r="K171" t="b">
+        <v>1</v>
+      </c>
+      <c r="L171" t="s">
+        <v>17</v>
+      </c>
+      <c r="M171" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>32</v>
+      </c>
+      <c r="B172" t="s">
+        <v>217</v>
+      </c>
+      <c r="C172" t="s">
+        <v>228</v>
+      </c>
+      <c r="D172" t="s">
+        <v>256</v>
+      </c>
+      <c r="E172" t="s">
+        <v>234</v>
+      </c>
+      <c r="F172" t="s">
+        <v>41</v>
+      </c>
+      <c r="G172" t="s">
+        <v>21</v>
+      </c>
+      <c r="H172" t="s">
+        <v>22</v>
+      </c>
+      <c r="I172" t="s">
+        <v>60</v>
+      </c>
+      <c r="J172" t="s">
+        <v>23</v>
+      </c>
+      <c r="K172" t="b">
+        <v>1</v>
+      </c>
+      <c r="L172" t="s">
+        <v>17</v>
+      </c>
+      <c r="M172" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>32</v>
+      </c>
+      <c r="B173" t="s">
+        <v>217</v>
+      </c>
+      <c r="C173" t="s">
+        <v>228</v>
+      </c>
+      <c r="D173" t="s">
+        <v>154</v>
+      </c>
+      <c r="E173" t="s">
+        <v>234</v>
+      </c>
+      <c r="F173" t="s">
+        <v>41</v>
+      </c>
+      <c r="G173" t="s">
+        <v>21</v>
+      </c>
+      <c r="H173" t="s">
+        <v>22</v>
+      </c>
+      <c r="I173" t="s">
+        <v>60</v>
+      </c>
+      <c r="J173" t="s">
+        <v>23</v>
+      </c>
+      <c r="K173" t="b">
+        <v>1</v>
+      </c>
+      <c r="L173" t="s">
+        <v>17</v>
+      </c>
+      <c r="M173" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>32</v>
+      </c>
+      <c r="B174" t="s">
+        <v>217</v>
+      </c>
+      <c r="C174" t="s">
+        <v>228</v>
+      </c>
+      <c r="D174" t="s">
+        <v>257</v>
+      </c>
+      <c r="E174" t="s">
+        <v>234</v>
+      </c>
+      <c r="F174" t="s">
+        <v>41</v>
+      </c>
+      <c r="G174" t="s">
+        <v>21</v>
+      </c>
+      <c r="H174" t="s">
+        <v>22</v>
+      </c>
+      <c r="I174" t="s">
+        <v>60</v>
+      </c>
+      <c r="J174" t="s">
+        <v>23</v>
+      </c>
+      <c r="K174" t="b">
+        <v>1</v>
+      </c>
+      <c r="L174" t="s">
+        <v>17</v>
+      </c>
+      <c r="M174" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>32</v>
+      </c>
+      <c r="B175" t="s">
+        <v>217</v>
+      </c>
+      <c r="C175" t="s">
+        <v>228</v>
+      </c>
+      <c r="D175" t="s">
+        <v>258</v>
+      </c>
+      <c r="E175" t="s">
+        <v>234</v>
+      </c>
+      <c r="F175" t="s">
+        <v>41</v>
+      </c>
+      <c r="G175" t="s">
+        <v>21</v>
+      </c>
+      <c r="H175" t="s">
+        <v>22</v>
+      </c>
+      <c r="I175" t="s">
+        <v>60</v>
+      </c>
+      <c r="J175" t="s">
+        <v>23</v>
+      </c>
+      <c r="K175" t="b">
+        <v>1</v>
+      </c>
+      <c r="L175" t="s">
+        <v>17</v>
+      </c>
+      <c r="M175" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>32</v>
+      </c>
+      <c r="B176" t="s">
+        <v>217</v>
+      </c>
+      <c r="C176" t="s">
+        <v>228</v>
+      </c>
+      <c r="D176" t="s">
+        <v>259</v>
+      </c>
+      <c r="E176" t="s">
+        <v>234</v>
+      </c>
+      <c r="F176" t="s">
+        <v>41</v>
+      </c>
+      <c r="G176" t="s">
+        <v>21</v>
+      </c>
+      <c r="H176" t="s">
+        <v>22</v>
+      </c>
+      <c r="I176" t="s">
+        <v>60</v>
+      </c>
+      <c r="J176" t="s">
+        <v>23</v>
+      </c>
+      <c r="K176" t="b">
+        <v>1</v>
+      </c>
+      <c r="L176" t="s">
+        <v>17</v>
+      </c>
+      <c r="M176" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>32</v>
+      </c>
+      <c r="B177" t="s">
+        <v>217</v>
+      </c>
+      <c r="C177" t="s">
+        <v>228</v>
+      </c>
+      <c r="D177" t="s">
+        <v>260</v>
+      </c>
+      <c r="E177" t="s">
+        <v>234</v>
+      </c>
+      <c r="F177" t="s">
+        <v>41</v>
+      </c>
+      <c r="G177" t="s">
+        <v>21</v>
+      </c>
+      <c r="H177" t="s">
+        <v>22</v>
+      </c>
+      <c r="I177" t="s">
+        <v>60</v>
+      </c>
+      <c r="J177" t="s">
+        <v>23</v>
+      </c>
+      <c r="K177" t="b">
+        <v>1</v>
+      </c>
+      <c r="L177" t="s">
+        <v>17</v>
+      </c>
+      <c r="M177" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>32</v>
+      </c>
+      <c r="B178" t="s">
+        <v>217</v>
+      </c>
+      <c r="C178" t="s">
+        <v>228</v>
+      </c>
+      <c r="D178" t="s">
+        <v>261</v>
+      </c>
+      <c r="E178" t="s">
+        <v>234</v>
+      </c>
+      <c r="F178" t="s">
+        <v>41</v>
+      </c>
+      <c r="G178" t="s">
+        <v>21</v>
+      </c>
+      <c r="H178" t="s">
+        <v>22</v>
+      </c>
+      <c r="I178" t="s">
+        <v>60</v>
+      </c>
+      <c r="J178" t="s">
+        <v>23</v>
+      </c>
+      <c r="K178" t="b">
+        <v>1</v>
+      </c>
+      <c r="L178" t="s">
+        <v>17</v>
+      </c>
+      <c r="M178" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>32</v>
+      </c>
+      <c r="B179" t="s">
+        <v>217</v>
+      </c>
+      <c r="C179" t="s">
+        <v>228</v>
+      </c>
+      <c r="D179" t="s">
+        <v>262</v>
+      </c>
+      <c r="E179" t="s">
+        <v>234</v>
+      </c>
+      <c r="F179" t="s">
+        <v>41</v>
+      </c>
+      <c r="G179" t="s">
+        <v>21</v>
+      </c>
+      <c r="H179" t="s">
+        <v>22</v>
+      </c>
+      <c r="I179" t="s">
+        <v>60</v>
+      </c>
+      <c r="J179" t="s">
+        <v>23</v>
+      </c>
+      <c r="K179" t="b">
+        <v>1</v>
+      </c>
+      <c r="L179" t="s">
+        <v>17</v>
+      </c>
+      <c r="M179" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>32</v>
+      </c>
+      <c r="B180" t="s">
+        <v>217</v>
+      </c>
+      <c r="C180" t="s">
+        <v>228</v>
+      </c>
+      <c r="D180" t="s">
+        <v>263</v>
+      </c>
+      <c r="E180" t="s">
+        <v>234</v>
+      </c>
+      <c r="F180" t="s">
+        <v>41</v>
+      </c>
+      <c r="G180" t="s">
+        <v>21</v>
+      </c>
+      <c r="H180" t="s">
+        <v>22</v>
+      </c>
+      <c r="I180" t="s">
+        <v>60</v>
+      </c>
+      <c r="J180" t="s">
+        <v>23</v>
+      </c>
+      <c r="K180" t="b">
+        <v>1</v>
+      </c>
+      <c r="L180" t="s">
+        <v>17</v>
+      </c>
+      <c r="M180" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>32</v>
+      </c>
+      <c r="B181" t="s">
+        <v>217</v>
+      </c>
+      <c r="C181" t="s">
+        <v>228</v>
+      </c>
+      <c r="D181" t="s">
+        <v>264</v>
+      </c>
+      <c r="E181" t="s">
+        <v>234</v>
+      </c>
+      <c r="F181" t="s">
+        <v>41</v>
+      </c>
+      <c r="G181" t="s">
+        <v>21</v>
+      </c>
+      <c r="H181" t="s">
+        <v>22</v>
+      </c>
+      <c r="I181" t="s">
+        <v>60</v>
+      </c>
+      <c r="J181" t="s">
+        <v>23</v>
+      </c>
+      <c r="K181" t="b">
+        <v>1</v>
+      </c>
+      <c r="L181" t="s">
+        <v>17</v>
+      </c>
+      <c r="M181" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>32</v>
+      </c>
+      <c r="B182" t="s">
+        <v>217</v>
+      </c>
+      <c r="C182" t="s">
+        <v>228</v>
+      </c>
+      <c r="D182" t="s">
+        <v>265</v>
+      </c>
+      <c r="E182" t="s">
+        <v>234</v>
+      </c>
+      <c r="F182" t="s">
+        <v>41</v>
+      </c>
+      <c r="G182" t="s">
+        <v>21</v>
+      </c>
+      <c r="H182" t="s">
+        <v>22</v>
+      </c>
+      <c r="I182" t="s">
+        <v>60</v>
+      </c>
+      <c r="J182" t="s">
+        <v>23</v>
+      </c>
+      <c r="K182" t="b">
+        <v>1</v>
+      </c>
+      <c r="L182" t="s">
+        <v>17</v>
+      </c>
+      <c r="M182" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>32</v>
+      </c>
+      <c r="B183" t="s">
+        <v>217</v>
+      </c>
+      <c r="C183" t="s">
+        <v>228</v>
+      </c>
+      <c r="D183" t="s">
+        <v>266</v>
+      </c>
+      <c r="E183" t="s">
+        <v>234</v>
+      </c>
+      <c r="F183" t="s">
+        <v>41</v>
+      </c>
+      <c r="G183" t="s">
+        <v>21</v>
+      </c>
+      <c r="H183" t="s">
+        <v>22</v>
+      </c>
+      <c r="I183" t="s">
+        <v>60</v>
+      </c>
+      <c r="J183" t="s">
+        <v>23</v>
+      </c>
+      <c r="K183" t="b">
+        <v>1</v>
+      </c>
+      <c r="L183" t="s">
+        <v>17</v>
+      </c>
+      <c r="M183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>32</v>
+      </c>
+      <c r="B184" t="s">
+        <v>217</v>
+      </c>
+      <c r="C184" t="s">
+        <v>228</v>
+      </c>
+      <c r="D184" t="s">
+        <v>267</v>
+      </c>
+      <c r="E184" t="s">
+        <v>234</v>
+      </c>
+      <c r="F184" t="s">
+        <v>41</v>
+      </c>
+      <c r="G184" t="s">
+        <v>21</v>
+      </c>
+      <c r="H184" t="s">
+        <v>22</v>
+      </c>
+      <c r="I184" t="s">
+        <v>60</v>
+      </c>
+      <c r="J184" t="s">
+        <v>23</v>
+      </c>
+      <c r="K184" t="b">
+        <v>1</v>
+      </c>
+      <c r="L184" t="s">
+        <v>17</v>
+      </c>
+      <c r="M184" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>32</v>
+      </c>
+      <c r="B185" t="s">
+        <v>217</v>
+      </c>
+      <c r="C185" t="s">
+        <v>228</v>
+      </c>
+      <c r="D185" t="s">
+        <v>268</v>
+      </c>
+      <c r="E185" t="s">
+        <v>234</v>
+      </c>
+      <c r="F185" t="s">
+        <v>41</v>
+      </c>
+      <c r="G185" t="s">
+        <v>21</v>
+      </c>
+      <c r="H185" t="s">
+        <v>22</v>
+      </c>
+      <c r="I185" t="s">
+        <v>60</v>
+      </c>
+      <c r="J185" t="s">
+        <v>23</v>
+      </c>
+      <c r="K185" t="b">
+        <v>1</v>
+      </c>
+      <c r="L185" t="s">
+        <v>17</v>
+      </c>
+      <c r="M185" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>32</v>
+      </c>
+      <c r="B186" t="s">
+        <v>217</v>
+      </c>
+      <c r="C186" t="s">
+        <v>228</v>
+      </c>
+      <c r="D186" t="s">
+        <v>269</v>
+      </c>
+      <c r="E186" t="s">
+        <v>234</v>
+      </c>
+      <c r="F186" t="s">
+        <v>41</v>
+      </c>
+      <c r="G186" t="s">
+        <v>21</v>
+      </c>
+      <c r="H186" t="s">
+        <v>22</v>
+      </c>
+      <c r="I186" t="s">
+        <v>60</v>
+      </c>
+      <c r="J186" t="s">
+        <v>23</v>
+      </c>
+      <c r="K186" t="b">
+        <v>1</v>
+      </c>
+      <c r="L186" t="s">
+        <v>17</v>
+      </c>
+      <c r="M186" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>32</v>
+      </c>
+      <c r="B187" t="s">
+        <v>217</v>
+      </c>
+      <c r="C187" t="s">
+        <v>228</v>
+      </c>
+      <c r="D187" t="s">
+        <v>270</v>
+      </c>
+      <c r="E187" t="s">
+        <v>234</v>
+      </c>
+      <c r="F187" t="s">
+        <v>41</v>
+      </c>
+      <c r="G187" t="s">
+        <v>21</v>
+      </c>
+      <c r="H187" t="s">
+        <v>22</v>
+      </c>
+      <c r="I187" t="s">
+        <v>60</v>
+      </c>
+      <c r="J187" t="s">
+        <v>23</v>
+      </c>
+      <c r="K187" t="b">
+        <v>1</v>
+      </c>
+      <c r="L187" t="s">
+        <v>17</v>
+      </c>
+      <c r="M187" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>32</v>
+      </c>
+      <c r="B188" t="s">
+        <v>217</v>
+      </c>
+      <c r="C188" t="s">
+        <v>228</v>
+      </c>
+      <c r="D188" t="s">
+        <v>271</v>
+      </c>
+      <c r="E188" t="s">
+        <v>234</v>
+      </c>
+      <c r="F188" t="s">
+        <v>41</v>
+      </c>
+      <c r="G188" t="s">
+        <v>21</v>
+      </c>
+      <c r="H188" t="s">
+        <v>22</v>
+      </c>
+      <c r="I188" t="s">
+        <v>60</v>
+      </c>
+      <c r="J188" t="s">
+        <v>23</v>
+      </c>
+      <c r="K188" t="b">
+        <v>1</v>
+      </c>
+      <c r="L188" t="s">
+        <v>17</v>
+      </c>
+      <c r="M188" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>32</v>
+      </c>
+      <c r="B189" t="s">
+        <v>272</v>
+      </c>
+      <c r="C189" t="s">
+        <v>273</v>
+      </c>
+      <c r="D189" t="s">
+        <v>274</v>
+      </c>
+      <c r="E189" t="s">
+        <v>287</v>
+      </c>
+      <c r="F189" t="s">
+        <v>41</v>
+      </c>
+      <c r="G189" t="s">
+        <v>21</v>
+      </c>
+      <c r="H189" t="s">
+        <v>22</v>
+      </c>
+      <c r="I189" t="s">
+        <v>60</v>
+      </c>
+      <c r="J189" t="s">
+        <v>23</v>
+      </c>
+      <c r="K189" t="b">
+        <v>1</v>
+      </c>
+      <c r="L189" t="s">
+        <v>17</v>
+      </c>
+      <c r="M189" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>32</v>
+      </c>
+      <c r="B190" t="s">
+        <v>272</v>
+      </c>
+      <c r="C190" t="s">
+        <v>273</v>
+      </c>
+      <c r="D190" t="s">
+        <v>276</v>
+      </c>
+      <c r="E190" t="s">
+        <v>287</v>
+      </c>
+      <c r="F190" t="s">
+        <v>41</v>
+      </c>
+      <c r="G190" t="s">
+        <v>21</v>
+      </c>
+      <c r="H190" t="s">
+        <v>22</v>
+      </c>
+      <c r="I190" t="s">
+        <v>60</v>
+      </c>
+      <c r="J190" t="s">
+        <v>23</v>
+      </c>
+      <c r="K190" t="b">
+        <v>1</v>
+      </c>
+      <c r="L190" t="s">
+        <v>17</v>
+      </c>
+      <c r="M190" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>32</v>
+      </c>
+      <c r="B191" t="s">
+        <v>272</v>
+      </c>
+      <c r="C191" t="s">
+        <v>273</v>
+      </c>
+      <c r="D191" t="s">
+        <v>277</v>
+      </c>
+      <c r="E191" t="s">
+        <v>287</v>
+      </c>
+      <c r="F191" t="s">
+        <v>41</v>
+      </c>
+      <c r="G191" t="s">
+        <v>21</v>
+      </c>
+      <c r="H191" t="s">
+        <v>22</v>
+      </c>
+      <c r="I191" t="s">
+        <v>60</v>
+      </c>
+      <c r="J191" t="s">
+        <v>23</v>
+      </c>
+      <c r="K191" t="b">
+        <v>1</v>
+      </c>
+      <c r="L191" t="s">
+        <v>17</v>
+      </c>
+      <c r="M191" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>32</v>
+      </c>
+      <c r="B192" t="s">
+        <v>272</v>
+      </c>
+      <c r="C192" t="s">
+        <v>273</v>
+      </c>
+      <c r="D192" t="s">
+        <v>278</v>
+      </c>
+      <c r="E192" t="s">
+        <v>287</v>
+      </c>
+      <c r="F192" t="s">
+        <v>41</v>
+      </c>
+      <c r="G192" t="s">
+        <v>21</v>
+      </c>
+      <c r="H192" t="s">
+        <v>22</v>
+      </c>
+      <c r="I192" t="s">
+        <v>60</v>
+      </c>
+      <c r="J192" t="s">
+        <v>23</v>
+      </c>
+      <c r="K192" t="b">
+        <v>1</v>
+      </c>
+      <c r="L192" t="s">
+        <v>17</v>
+      </c>
+      <c r="M192" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>32</v>
+      </c>
+      <c r="B193" t="s">
+        <v>272</v>
+      </c>
+      <c r="C193" t="s">
+        <v>273</v>
+      </c>
+      <c r="D193" t="s">
+        <v>279</v>
+      </c>
+      <c r="E193" t="s">
+        <v>287</v>
+      </c>
+      <c r="F193" t="s">
+        <v>41</v>
+      </c>
+      <c r="G193" t="s">
+        <v>21</v>
+      </c>
+      <c r="H193" t="s">
+        <v>22</v>
+      </c>
+      <c r="I193" t="s">
+        <v>60</v>
+      </c>
+      <c r="J193" t="s">
+        <v>23</v>
+      </c>
+      <c r="K193" t="b">
+        <v>1</v>
+      </c>
+      <c r="L193" t="s">
+        <v>17</v>
+      </c>
+      <c r="M193" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>32</v>
+      </c>
+      <c r="B194" t="s">
+        <v>272</v>
+      </c>
+      <c r="C194" t="s">
+        <v>273</v>
+      </c>
+      <c r="D194" t="s">
+        <v>275</v>
+      </c>
+      <c r="E194" t="s">
+        <v>287</v>
+      </c>
+      <c r="F194" t="s">
+        <v>41</v>
+      </c>
+      <c r="G194" t="s">
+        <v>21</v>
+      </c>
+      <c r="H194" t="s">
+        <v>22</v>
+      </c>
+      <c r="I194" t="s">
+        <v>60</v>
+      </c>
+      <c r="J194" t="s">
+        <v>23</v>
+      </c>
+      <c r="K194" t="b">
+        <v>1</v>
+      </c>
+      <c r="L194" t="s">
+        <v>17</v>
+      </c>
+      <c r="M194" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>32</v>
+      </c>
+      <c r="B195" t="s">
+        <v>272</v>
+      </c>
+      <c r="C195" t="s">
+        <v>273</v>
+      </c>
+      <c r="D195" t="s">
+        <v>280</v>
+      </c>
+      <c r="E195" t="s">
+        <v>287</v>
+      </c>
+      <c r="F195" t="s">
+        <v>41</v>
+      </c>
+      <c r="G195" t="s">
+        <v>21</v>
+      </c>
+      <c r="H195" t="s">
+        <v>22</v>
+      </c>
+      <c r="I195" t="s">
+        <v>60</v>
+      </c>
+      <c r="J195" t="s">
+        <v>23</v>
+      </c>
+      <c r="K195" t="b">
+        <v>1</v>
+      </c>
+      <c r="L195" t="s">
+        <v>17</v>
+      </c>
+      <c r="M195" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>32</v>
+      </c>
+      <c r="B196" t="s">
+        <v>272</v>
+      </c>
+      <c r="C196" t="s">
+        <v>273</v>
+      </c>
+      <c r="D196" t="s">
+        <v>281</v>
+      </c>
+      <c r="E196" t="s">
+        <v>287</v>
+      </c>
+      <c r="F196" t="s">
+        <v>41</v>
+      </c>
+      <c r="G196" t="s">
+        <v>21</v>
+      </c>
+      <c r="H196" t="s">
+        <v>22</v>
+      </c>
+      <c r="I196" t="s">
+        <v>60</v>
+      </c>
+      <c r="J196" t="s">
+        <v>23</v>
+      </c>
+      <c r="K196" t="b">
+        <v>1</v>
+      </c>
+      <c r="L196" t="s">
+        <v>17</v>
+      </c>
+      <c r="M196" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>32</v>
+      </c>
+      <c r="B197" t="s">
+        <v>272</v>
+      </c>
+      <c r="C197" t="s">
+        <v>273</v>
+      </c>
+      <c r="D197" t="s">
+        <v>282</v>
+      </c>
+      <c r="E197" t="s">
+        <v>287</v>
+      </c>
+      <c r="F197" t="s">
+        <v>41</v>
+      </c>
+      <c r="G197" t="s">
+        <v>21</v>
+      </c>
+      <c r="H197" t="s">
+        <v>22</v>
+      </c>
+      <c r="I197" t="s">
+        <v>60</v>
+      </c>
+      <c r="J197" t="s">
+        <v>23</v>
+      </c>
+      <c r="K197" t="b">
+        <v>1</v>
+      </c>
+      <c r="L197" t="s">
+        <v>17</v>
+      </c>
+      <c r="M197" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>32</v>
+      </c>
+      <c r="B198" t="s">
+        <v>272</v>
+      </c>
+      <c r="C198" t="s">
+        <v>273</v>
+      </c>
+      <c r="D198" t="s">
+        <v>283</v>
+      </c>
+      <c r="E198" t="s">
+        <v>287</v>
+      </c>
+      <c r="F198" t="s">
+        <v>41</v>
+      </c>
+      <c r="G198" t="s">
+        <v>21</v>
+      </c>
+      <c r="H198" t="s">
+        <v>22</v>
+      </c>
+      <c r="I198" t="s">
+        <v>60</v>
+      </c>
+      <c r="J198" t="s">
+        <v>23</v>
+      </c>
+      <c r="K198" t="b">
+        <v>1</v>
+      </c>
+      <c r="L198" t="s">
+        <v>17</v>
+      </c>
+      <c r="M198" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>32</v>
+      </c>
+      <c r="B199" t="s">
+        <v>272</v>
+      </c>
+      <c r="C199" t="s">
+        <v>273</v>
+      </c>
+      <c r="D199" t="s">
+        <v>284</v>
+      </c>
+      <c r="E199" t="s">
+        <v>287</v>
+      </c>
+      <c r="F199" t="s">
+        <v>41</v>
+      </c>
+      <c r="G199" t="s">
+        <v>21</v>
+      </c>
+      <c r="H199" t="s">
+        <v>22</v>
+      </c>
+      <c r="I199" t="s">
+        <v>60</v>
+      </c>
+      <c r="J199" t="s">
+        <v>23</v>
+      </c>
+      <c r="K199" t="b">
+        <v>1</v>
+      </c>
+      <c r="L199" t="s">
+        <v>17</v>
+      </c>
+      <c r="M199" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>32</v>
+      </c>
+      <c r="B200" t="s">
+        <v>272</v>
+      </c>
+      <c r="C200" t="s">
+        <v>273</v>
+      </c>
+      <c r="D200" t="s">
+        <v>285</v>
+      </c>
+      <c r="E200" t="s">
+        <v>287</v>
+      </c>
+      <c r="F200" t="s">
+        <v>41</v>
+      </c>
+      <c r="G200" t="s">
+        <v>21</v>
+      </c>
+      <c r="H200" t="s">
+        <v>22</v>
+      </c>
+      <c r="I200" t="s">
+        <v>60</v>
+      </c>
+      <c r="J200" t="s">
+        <v>23</v>
+      </c>
+      <c r="K200" t="b">
+        <v>1</v>
+      </c>
+      <c r="L200" t="s">
+        <v>17</v>
+      </c>
+      <c r="M200" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>32</v>
+      </c>
+      <c r="B201" t="s">
+        <v>272</v>
+      </c>
+      <c r="C201" t="s">
+        <v>273</v>
+      </c>
+      <c r="D201" t="s">
+        <v>286</v>
+      </c>
+      <c r="E201" t="s">
+        <v>287</v>
+      </c>
+      <c r="F201" t="s">
+        <v>41</v>
+      </c>
+      <c r="G201" t="s">
+        <v>21</v>
+      </c>
+      <c r="H201" t="s">
+        <v>22</v>
+      </c>
+      <c r="I201" t="s">
+        <v>60</v>
+      </c>
+      <c r="J201" t="s">
+        <v>23</v>
+      </c>
+      <c r="K201" t="b">
+        <v>1</v>
+      </c>
+      <c r="L201" t="s">
+        <v>17</v>
+      </c>
+      <c r="M201" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>32</v>
+      </c>
+      <c r="B202" t="s">
+        <v>272</v>
+      </c>
+      <c r="C202" t="s">
+        <v>288</v>
+      </c>
+      <c r="D202" t="s">
+        <v>289</v>
+      </c>
+      <c r="E202" t="s">
+        <v>306</v>
+      </c>
+      <c r="F202" t="s">
+        <v>41</v>
+      </c>
+      <c r="G202" t="s">
+        <v>21</v>
+      </c>
+      <c r="H202" t="s">
+        <v>22</v>
+      </c>
+      <c r="I202" t="s">
+        <v>60</v>
+      </c>
+      <c r="J202" t="s">
+        <v>23</v>
+      </c>
+      <c r="K202" t="b">
+        <v>1</v>
+      </c>
+      <c r="L202" t="s">
+        <v>17</v>
+      </c>
+      <c r="M202" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>32</v>
+      </c>
+      <c r="B203" t="s">
+        <v>272</v>
+      </c>
+      <c r="C203" t="s">
+        <v>288</v>
+      </c>
+      <c r="D203" t="s">
+        <v>290</v>
+      </c>
+      <c r="E203" t="s">
+        <v>306</v>
+      </c>
+      <c r="F203" t="s">
+        <v>41</v>
+      </c>
+      <c r="G203" t="s">
+        <v>21</v>
+      </c>
+      <c r="H203" t="s">
+        <v>22</v>
+      </c>
+      <c r="I203" t="s">
+        <v>60</v>
+      </c>
+      <c r="J203" t="s">
+        <v>23</v>
+      </c>
+      <c r="K203" t="b">
+        <v>1</v>
+      </c>
+      <c r="L203" t="s">
+        <v>17</v>
+      </c>
+      <c r="M203" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>32</v>
+      </c>
+      <c r="B204" t="s">
+        <v>272</v>
+      </c>
+      <c r="C204" t="s">
+        <v>288</v>
+      </c>
+      <c r="D204" t="s">
+        <v>291</v>
+      </c>
+      <c r="E204" t="s">
+        <v>306</v>
+      </c>
+      <c r="F204" t="s">
+        <v>41</v>
+      </c>
+      <c r="G204" t="s">
+        <v>21</v>
+      </c>
+      <c r="H204" t="s">
+        <v>22</v>
+      </c>
+      <c r="I204" t="s">
+        <v>60</v>
+      </c>
+      <c r="J204" t="s">
+        <v>23</v>
+      </c>
+      <c r="K204" t="b">
+        <v>1</v>
+      </c>
+      <c r="L204" t="s">
+        <v>17</v>
+      </c>
+      <c r="M204" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>32</v>
+      </c>
+      <c r="B205" t="s">
+        <v>272</v>
+      </c>
+      <c r="C205" t="s">
+        <v>288</v>
+      </c>
+      <c r="D205" t="s">
+        <v>292</v>
+      </c>
+      <c r="E205" t="s">
+        <v>306</v>
+      </c>
+      <c r="F205" t="s">
+        <v>41</v>
+      </c>
+      <c r="G205" t="s">
+        <v>21</v>
+      </c>
+      <c r="H205" t="s">
+        <v>22</v>
+      </c>
+      <c r="I205" t="s">
+        <v>60</v>
+      </c>
+      <c r="J205" t="s">
+        <v>23</v>
+      </c>
+      <c r="K205" t="b">
+        <v>1</v>
+      </c>
+      <c r="L205" t="s">
+        <v>17</v>
+      </c>
+      <c r="M205" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>32</v>
+      </c>
+      <c r="B206" t="s">
+        <v>272</v>
+      </c>
+      <c r="C206" t="s">
+        <v>288</v>
+      </c>
+      <c r="D206" t="s">
+        <v>293</v>
+      </c>
+      <c r="E206" t="s">
+        <v>306</v>
+      </c>
+      <c r="F206" t="s">
+        <v>41</v>
+      </c>
+      <c r="G206" t="s">
+        <v>21</v>
+      </c>
+      <c r="H206" t="s">
+        <v>22</v>
+      </c>
+      <c r="I206" t="s">
+        <v>60</v>
+      </c>
+      <c r="J206" t="s">
+        <v>23</v>
+      </c>
+      <c r="K206" t="b">
+        <v>1</v>
+      </c>
+      <c r="L206" t="s">
+        <v>17</v>
+      </c>
+      <c r="M206" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>32</v>
+      </c>
+      <c r="B207" t="s">
+        <v>272</v>
+      </c>
+      <c r="C207" t="s">
+        <v>288</v>
+      </c>
+      <c r="D207" t="s">
+        <v>294</v>
+      </c>
+      <c r="E207" t="s">
+        <v>306</v>
+      </c>
+      <c r="F207" t="s">
+        <v>41</v>
+      </c>
+      <c r="G207" t="s">
+        <v>21</v>
+      </c>
+      <c r="H207" t="s">
+        <v>22</v>
+      </c>
+      <c r="I207" t="s">
+        <v>60</v>
+      </c>
+      <c r="J207" t="s">
+        <v>23</v>
+      </c>
+      <c r="K207" t="b">
+        <v>1</v>
+      </c>
+      <c r="L207" t="s">
+        <v>17</v>
+      </c>
+      <c r="M207" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>32</v>
+      </c>
+      <c r="B208" t="s">
+        <v>272</v>
+      </c>
+      <c r="C208" t="s">
+        <v>288</v>
+      </c>
+      <c r="D208" t="s">
+        <v>295</v>
+      </c>
+      <c r="E208" t="s">
+        <v>306</v>
+      </c>
+      <c r="F208" t="s">
+        <v>41</v>
+      </c>
+      <c r="G208" t="s">
+        <v>21</v>
+      </c>
+      <c r="H208" t="s">
+        <v>22</v>
+      </c>
+      <c r="I208" t="s">
+        <v>60</v>
+      </c>
+      <c r="J208" t="s">
+        <v>23</v>
+      </c>
+      <c r="K208" t="b">
+        <v>1</v>
+      </c>
+      <c r="L208" t="s">
+        <v>17</v>
+      </c>
+      <c r="M208" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>32</v>
+      </c>
+      <c r="B209" t="s">
+        <v>272</v>
+      </c>
+      <c r="C209" t="s">
+        <v>288</v>
+      </c>
+      <c r="D209" t="s">
+        <v>296</v>
+      </c>
+      <c r="E209" t="s">
+        <v>306</v>
+      </c>
+      <c r="F209" t="s">
+        <v>41</v>
+      </c>
+      <c r="G209" t="s">
+        <v>21</v>
+      </c>
+      <c r="H209" t="s">
+        <v>22</v>
+      </c>
+      <c r="I209" t="s">
+        <v>60</v>
+      </c>
+      <c r="J209" t="s">
+        <v>23</v>
+      </c>
+      <c r="K209" t="b">
+        <v>1</v>
+      </c>
+      <c r="L209" t="s">
+        <v>17</v>
+      </c>
+      <c r="M209" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>32</v>
+      </c>
+      <c r="B210" t="s">
+        <v>272</v>
+      </c>
+      <c r="C210" t="s">
+        <v>288</v>
+      </c>
+      <c r="D210" t="s">
+        <v>297</v>
+      </c>
+      <c r="E210" t="s">
+        <v>306</v>
+      </c>
+      <c r="F210" t="s">
+        <v>41</v>
+      </c>
+      <c r="G210" t="s">
+        <v>21</v>
+      </c>
+      <c r="H210" t="s">
+        <v>22</v>
+      </c>
+      <c r="I210" t="s">
+        <v>60</v>
+      </c>
+      <c r="J210" t="s">
+        <v>23</v>
+      </c>
+      <c r="K210" t="b">
+        <v>1</v>
+      </c>
+      <c r="L210" t="s">
+        <v>17</v>
+      </c>
+      <c r="M210" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>32</v>
+      </c>
+      <c r="B211" t="s">
+        <v>272</v>
+      </c>
+      <c r="C211" t="s">
+        <v>288</v>
+      </c>
+      <c r="D211" t="s">
+        <v>298</v>
+      </c>
+      <c r="E211" t="s">
+        <v>306</v>
+      </c>
+      <c r="F211" t="s">
+        <v>41</v>
+      </c>
+      <c r="G211" t="s">
+        <v>21</v>
+      </c>
+      <c r="H211" t="s">
+        <v>22</v>
+      </c>
+      <c r="I211" t="s">
+        <v>60</v>
+      </c>
+      <c r="J211" t="s">
+        <v>23</v>
+      </c>
+      <c r="K211" t="b">
+        <v>1</v>
+      </c>
+      <c r="L211" t="s">
+        <v>17</v>
+      </c>
+      <c r="M211" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>32</v>
+      </c>
+      <c r="B212" t="s">
+        <v>272</v>
+      </c>
+      <c r="C212" t="s">
+        <v>288</v>
+      </c>
+      <c r="D212" t="s">
+        <v>299</v>
+      </c>
+      <c r="E212" t="s">
+        <v>306</v>
+      </c>
+      <c r="F212" t="s">
+        <v>41</v>
+      </c>
+      <c r="G212" t="s">
+        <v>21</v>
+      </c>
+      <c r="H212" t="s">
+        <v>22</v>
+      </c>
+      <c r="I212" t="s">
+        <v>60</v>
+      </c>
+      <c r="J212" t="s">
+        <v>23</v>
+      </c>
+      <c r="K212" t="b">
+        <v>1</v>
+      </c>
+      <c r="L212" t="s">
+        <v>17</v>
+      </c>
+      <c r="M212" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>32</v>
+      </c>
+      <c r="B213" t="s">
+        <v>272</v>
+      </c>
+      <c r="C213" t="s">
+        <v>288</v>
+      </c>
+      <c r="D213" t="s">
+        <v>300</v>
+      </c>
+      <c r="E213" t="s">
+        <v>306</v>
+      </c>
+      <c r="F213" t="s">
+        <v>41</v>
+      </c>
+      <c r="G213" t="s">
+        <v>21</v>
+      </c>
+      <c r="H213" t="s">
+        <v>22</v>
+      </c>
+      <c r="I213" t="s">
+        <v>60</v>
+      </c>
+      <c r="J213" t="s">
+        <v>23</v>
+      </c>
+      <c r="K213" t="b">
+        <v>1</v>
+      </c>
+      <c r="L213" t="s">
+        <v>17</v>
+      </c>
+      <c r="M213" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>32</v>
+      </c>
+      <c r="B214" t="s">
+        <v>272</v>
+      </c>
+      <c r="C214" t="s">
+        <v>288</v>
+      </c>
+      <c r="D214" t="s">
+        <v>301</v>
+      </c>
+      <c r="E214" t="s">
+        <v>306</v>
+      </c>
+      <c r="F214" t="s">
+        <v>41</v>
+      </c>
+      <c r="G214" t="s">
+        <v>21</v>
+      </c>
+      <c r="H214" t="s">
+        <v>22</v>
+      </c>
+      <c r="I214" t="s">
+        <v>60</v>
+      </c>
+      <c r="J214" t="s">
+        <v>23</v>
+      </c>
+      <c r="K214" t="b">
+        <v>1</v>
+      </c>
+      <c r="L214" t="s">
+        <v>17</v>
+      </c>
+      <c r="M214" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>32</v>
+      </c>
+      <c r="B215" t="s">
+        <v>272</v>
+      </c>
+      <c r="C215" t="s">
+        <v>288</v>
+      </c>
+      <c r="D215" t="s">
+        <v>302</v>
+      </c>
+      <c r="E215" t="s">
+        <v>306</v>
+      </c>
+      <c r="F215" t="s">
+        <v>41</v>
+      </c>
+      <c r="G215" t="s">
+        <v>21</v>
+      </c>
+      <c r="H215" t="s">
+        <v>22</v>
+      </c>
+      <c r="I215" t="s">
+        <v>60</v>
+      </c>
+      <c r="J215" t="s">
+        <v>23</v>
+      </c>
+      <c r="K215" t="b">
+        <v>1</v>
+      </c>
+      <c r="L215" t="s">
+        <v>17</v>
+      </c>
+      <c r="M215" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>32</v>
+      </c>
+      <c r="B216" t="s">
+        <v>272</v>
+      </c>
+      <c r="C216" t="s">
+        <v>288</v>
+      </c>
+      <c r="D216" t="s">
+        <v>303</v>
+      </c>
+      <c r="E216" t="s">
+        <v>306</v>
+      </c>
+      <c r="F216" t="s">
+        <v>41</v>
+      </c>
+      <c r="G216" t="s">
+        <v>21</v>
+      </c>
+      <c r="H216" t="s">
+        <v>22</v>
+      </c>
+      <c r="I216" t="s">
+        <v>60</v>
+      </c>
+      <c r="J216" t="s">
+        <v>23</v>
+      </c>
+      <c r="K216" t="b">
+        <v>1</v>
+      </c>
+      <c r="L216" t="s">
+        <v>17</v>
+      </c>
+      <c r="M216" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>32</v>
+      </c>
+      <c r="B217" t="s">
+        <v>272</v>
+      </c>
+      <c r="C217" t="s">
+        <v>288</v>
+      </c>
+      <c r="D217" t="s">
+        <v>304</v>
+      </c>
+      <c r="E217" t="s">
+        <v>306</v>
+      </c>
+      <c r="F217" t="s">
+        <v>41</v>
+      </c>
+      <c r="G217" t="s">
+        <v>21</v>
+      </c>
+      <c r="H217" t="s">
+        <v>22</v>
+      </c>
+      <c r="I217" t="s">
+        <v>60</v>
+      </c>
+      <c r="J217" t="s">
+        <v>23</v>
+      </c>
+      <c r="K217" t="b">
+        <v>1</v>
+      </c>
+      <c r="L217" t="s">
+        <v>17</v>
+      </c>
+      <c r="M217" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>32</v>
+      </c>
+      <c r="B218" t="s">
+        <v>272</v>
+      </c>
+      <c r="C218" t="s">
+        <v>288</v>
+      </c>
+      <c r="D218" t="s">
+        <v>305</v>
+      </c>
+      <c r="E218" t="s">
+        <v>306</v>
+      </c>
+      <c r="F218" t="s">
+        <v>41</v>
+      </c>
+      <c r="G218" t="s">
+        <v>21</v>
+      </c>
+      <c r="H218" t="s">
+        <v>22</v>
+      </c>
+      <c r="I218" t="s">
+        <v>60</v>
+      </c>
+      <c r="J218" t="s">
+        <v>23</v>
+      </c>
+      <c r="K218" t="b">
+        <v>1</v>
+      </c>
+      <c r="L218" t="s">
+        <v>17</v>
+      </c>
+      <c r="M218" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>37</v>
+      </c>
+      <c r="B219" t="s">
+        <v>307</v>
+      </c>
+      <c r="C219" t="s">
+        <v>308</v>
+      </c>
+      <c r="D219" t="s">
+        <v>309</v>
+      </c>
+      <c r="E219" t="s">
+        <v>310</v>
+      </c>
+      <c r="F219" t="s">
+        <v>41</v>
+      </c>
+      <c r="G219" t="s">
+        <v>21</v>
+      </c>
+      <c r="H219" t="s">
+        <v>22</v>
+      </c>
+      <c r="I219" t="s">
+        <v>60</v>
+      </c>
+      <c r="J219" t="s">
+        <v>23</v>
+      </c>
+      <c r="K219" t="b">
+        <v>1</v>
+      </c>
+      <c r="L219" t="s">
+        <v>17</v>
+      </c>
+      <c r="M219" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>37</v>
+      </c>
+      <c r="B220" t="s">
+        <v>307</v>
+      </c>
+      <c r="C220" t="s">
+        <v>308</v>
+      </c>
+      <c r="D220" t="s">
+        <v>311</v>
+      </c>
+      <c r="E220" t="s">
+        <v>310</v>
+      </c>
+      <c r="F220" t="s">
+        <v>41</v>
+      </c>
+      <c r="G220" t="s">
+        <v>21</v>
+      </c>
+      <c r="H220" t="s">
+        <v>22</v>
+      </c>
+      <c r="I220" t="s">
+        <v>60</v>
+      </c>
+      <c r="J220" t="s">
+        <v>23</v>
+      </c>
+      <c r="K220" t="b">
+        <v>1</v>
+      </c>
+      <c r="L220" t="s">
+        <v>17</v>
+      </c>
+      <c r="M220" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>37</v>
+      </c>
+      <c r="B221" t="s">
+        <v>307</v>
+      </c>
+      <c r="C221" t="s">
+        <v>308</v>
+      </c>
+      <c r="D221" t="s">
+        <v>312</v>
+      </c>
+      <c r="E221" t="s">
+        <v>310</v>
+      </c>
+      <c r="F221" t="s">
+        <v>41</v>
+      </c>
+      <c r="G221" t="s">
+        <v>21</v>
+      </c>
+      <c r="H221" t="s">
+        <v>22</v>
+      </c>
+      <c r="I221" t="s">
+        <v>60</v>
+      </c>
+      <c r="J221" t="s">
+        <v>23</v>
+      </c>
+      <c r="K221" t="b">
+        <v>1</v>
+      </c>
+      <c r="L221" t="s">
+        <v>17</v>
+      </c>
+      <c r="M221" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>37</v>
+      </c>
+      <c r="B222" t="s">
+        <v>307</v>
+      </c>
+      <c r="C222" t="s">
+        <v>308</v>
+      </c>
+      <c r="D222" t="s">
+        <v>313</v>
+      </c>
+      <c r="E222" t="s">
+        <v>310</v>
+      </c>
+      <c r="F222" t="s">
+        <v>41</v>
+      </c>
+      <c r="G222" t="s">
+        <v>21</v>
+      </c>
+      <c r="H222" t="s">
+        <v>22</v>
+      </c>
+      <c r="I222" t="s">
+        <v>60</v>
+      </c>
+      <c r="J222" t="s">
+        <v>23</v>
+      </c>
+      <c r="K222" t="b">
+        <v>1</v>
+      </c>
+      <c r="L222" t="s">
+        <v>17</v>
+      </c>
+      <c r="M222" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>37</v>
+      </c>
+      <c r="B223" t="s">
+        <v>307</v>
+      </c>
+      <c r="C223" t="s">
+        <v>308</v>
+      </c>
+      <c r="D223" t="s">
+        <v>314</v>
+      </c>
+      <c r="E223" t="s">
+        <v>310</v>
+      </c>
+      <c r="F223" t="s">
+        <v>41</v>
+      </c>
+      <c r="G223" t="s">
+        <v>21</v>
+      </c>
+      <c r="H223" t="s">
+        <v>22</v>
+      </c>
+      <c r="I223" t="s">
+        <v>60</v>
+      </c>
+      <c r="J223" t="s">
+        <v>23</v>
+      </c>
+      <c r="K223" t="b">
+        <v>1</v>
+      </c>
+      <c r="L223" t="s">
+        <v>17</v>
+      </c>
+      <c r="M223" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>37</v>
+      </c>
+      <c r="B224" t="s">
+        <v>307</v>
+      </c>
+      <c r="C224" t="s">
+        <v>308</v>
+      </c>
+      <c r="D224" t="s">
+        <v>315</v>
+      </c>
+      <c r="E224" t="s">
+        <v>310</v>
+      </c>
+      <c r="F224" t="s">
+        <v>41</v>
+      </c>
+      <c r="G224" t="s">
+        <v>21</v>
+      </c>
+      <c r="H224" t="s">
+        <v>22</v>
+      </c>
+      <c r="I224" t="s">
+        <v>60</v>
+      </c>
+      <c r="J224" t="s">
+        <v>23</v>
+      </c>
+      <c r="K224" t="b">
+        <v>1</v>
+      </c>
+      <c r="L224" t="s">
+        <v>17</v>
+      </c>
+      <c r="M224" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>37</v>
+      </c>
+      <c r="B225" t="s">
+        <v>307</v>
+      </c>
+      <c r="C225" t="s">
+        <v>308</v>
+      </c>
+      <c r="D225" t="s">
+        <v>316</v>
+      </c>
+      <c r="E225" t="s">
+        <v>310</v>
+      </c>
+      <c r="F225" t="s">
+        <v>41</v>
+      </c>
+      <c r="G225" t="s">
+        <v>21</v>
+      </c>
+      <c r="H225" t="s">
+        <v>22</v>
+      </c>
+      <c r="I225" t="s">
+        <v>60</v>
+      </c>
+      <c r="J225" t="s">
+        <v>23</v>
+      </c>
+      <c r="K225" t="b">
+        <v>1</v>
+      </c>
+      <c r="L225" t="s">
+        <v>17</v>
+      </c>
+      <c r="M225" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>37</v>
+      </c>
+      <c r="B226" t="s">
+        <v>307</v>
+      </c>
+      <c r="C226" t="s">
+        <v>308</v>
+      </c>
+      <c r="D226" t="s">
+        <v>317</v>
+      </c>
+      <c r="E226" t="s">
+        <v>310</v>
+      </c>
+      <c r="F226" t="s">
+        <v>41</v>
+      </c>
+      <c r="G226" t="s">
+        <v>21</v>
+      </c>
+      <c r="H226" t="s">
+        <v>22</v>
+      </c>
+      <c r="I226" t="s">
+        <v>60</v>
+      </c>
+      <c r="J226" t="s">
+        <v>23</v>
+      </c>
+      <c r="K226" t="b">
+        <v>1</v>
+      </c>
+      <c r="L226" t="s">
+        <v>17</v>
+      </c>
+      <c r="M226" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>37</v>
+      </c>
+      <c r="B227" t="s">
+        <v>307</v>
+      </c>
+      <c r="C227" t="s">
+        <v>308</v>
+      </c>
+      <c r="D227" t="s">
+        <v>318</v>
+      </c>
+      <c r="E227" t="s">
+        <v>310</v>
+      </c>
+      <c r="F227" t="s">
+        <v>41</v>
+      </c>
+      <c r="G227" t="s">
+        <v>21</v>
+      </c>
+      <c r="H227" t="s">
+        <v>22</v>
+      </c>
+      <c r="I227" t="s">
+        <v>60</v>
+      </c>
+      <c r="J227" t="s">
+        <v>23</v>
+      </c>
+      <c r="K227" t="b">
+        <v>1</v>
+      </c>
+      <c r="L227" t="s">
+        <v>17</v>
+      </c>
+      <c r="M227" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>37</v>
+      </c>
+      <c r="B228" t="s">
+        <v>307</v>
+      </c>
+      <c r="C228" t="s">
+        <v>308</v>
+      </c>
+      <c r="D228" t="s">
+        <v>319</v>
+      </c>
+      <c r="E228" t="s">
+        <v>310</v>
+      </c>
+      <c r="F228" t="s">
+        <v>41</v>
+      </c>
+      <c r="G228" t="s">
+        <v>21</v>
+      </c>
+      <c r="H228" t="s">
+        <v>22</v>
+      </c>
+      <c r="I228" t="s">
+        <v>60</v>
+      </c>
+      <c r="J228" t="s">
+        <v>23</v>
+      </c>
+      <c r="K228" t="b">
+        <v>1</v>
+      </c>
+      <c r="L228" t="s">
+        <v>17</v>
+      </c>
+      <c r="M228" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>37</v>
+      </c>
+      <c r="B229" t="s">
+        <v>307</v>
+      </c>
+      <c r="C229" t="s">
+        <v>308</v>
+      </c>
+      <c r="D229" t="s">
+        <v>320</v>
+      </c>
+      <c r="E229" t="s">
+        <v>310</v>
+      </c>
+      <c r="F229" t="s">
+        <v>41</v>
+      </c>
+      <c r="G229" t="s">
+        <v>21</v>
+      </c>
+      <c r="H229" t="s">
+        <v>22</v>
+      </c>
+      <c r="I229" t="s">
+        <v>60</v>
+      </c>
+      <c r="J229" t="s">
+        <v>23</v>
+      </c>
+      <c r="K229" t="b">
+        <v>1</v>
+      </c>
+      <c r="L229" t="s">
+        <v>17</v>
+      </c>
+      <c r="M229" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>37</v>
+      </c>
+      <c r="B230" t="s">
+        <v>307</v>
+      </c>
+      <c r="C230" t="s">
+        <v>308</v>
+      </c>
+      <c r="D230" t="s">
+        <v>321</v>
+      </c>
+      <c r="E230" t="s">
+        <v>310</v>
+      </c>
+      <c r="F230" t="s">
+        <v>41</v>
+      </c>
+      <c r="G230" t="s">
+        <v>21</v>
+      </c>
+      <c r="H230" t="s">
+        <v>22</v>
+      </c>
+      <c r="I230" t="s">
+        <v>60</v>
+      </c>
+      <c r="J230" t="s">
+        <v>23</v>
+      </c>
+      <c r="K230" t="b">
+        <v>1</v>
+      </c>
+      <c r="L230" t="s">
+        <v>17</v>
+      </c>
+      <c r="M230" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>37</v>
+      </c>
+      <c r="B231" t="s">
+        <v>307</v>
+      </c>
+      <c r="C231" t="s">
+        <v>308</v>
+      </c>
+      <c r="D231" t="s">
+        <v>322</v>
+      </c>
+      <c r="E231" t="s">
+        <v>310</v>
+      </c>
+      <c r="F231" t="s">
+        <v>41</v>
+      </c>
+      <c r="G231" t="s">
+        <v>21</v>
+      </c>
+      <c r="H231" t="s">
+        <v>22</v>
+      </c>
+      <c r="I231" t="s">
+        <v>60</v>
+      </c>
+      <c r="J231" t="s">
+        <v>23</v>
+      </c>
+      <c r="K231" t="b">
+        <v>1</v>
+      </c>
+      <c r="L231" t="s">
+        <v>17</v>
+      </c>
+      <c r="M231" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>37</v>
+      </c>
+      <c r="B232" t="s">
+        <v>307</v>
+      </c>
+      <c r="C232" t="s">
+        <v>308</v>
+      </c>
+      <c r="D232" t="s">
+        <v>323</v>
+      </c>
+      <c r="E232" t="s">
+        <v>310</v>
+      </c>
+      <c r="F232" t="s">
+        <v>41</v>
+      </c>
+      <c r="G232" t="s">
+        <v>21</v>
+      </c>
+      <c r="H232" t="s">
+        <v>22</v>
+      </c>
+      <c r="I232" t="s">
+        <v>60</v>
+      </c>
+      <c r="J232" t="s">
+        <v>23</v>
+      </c>
+      <c r="K232" t="b">
+        <v>1</v>
+      </c>
+      <c r="L232" t="s">
+        <v>17</v>
+      </c>
+      <c r="M232" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K500" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K499" xr:uid="{00000000-0002-0000-0000-00000A000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3964,43 +10667,43 @@
           <x14:formula1>
             <xm:f>RefData!$A$1:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A500</xm:sqref>
+          <xm:sqref>A2:A499</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>RefData!$B$1:$B$17</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F500</xm:sqref>
+          <xm:sqref>F2:F499</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
             <xm:f>RefData!$C$1:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G500</xm:sqref>
+          <xm:sqref>G2:G499</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
             <xm:f>RefData!$D$1:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H500</xm:sqref>
+          <xm:sqref>H2:H499</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000008000000}">
           <x14:formula1>
             <xm:f>RefData!$E$1:$E$7</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J500</xm:sqref>
+          <xm:sqref>J2:J499</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
           <x14:formula1>
             <xm:f>RefData!$F$1:$F$2</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L500</xm:sqref>
+          <xm:sqref>L2:L499</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
           <x14:formula1>
             <xm:f>RefData!$G$1:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M500</xm:sqref>
+          <xm:sqref>M2:M499</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
